--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://depedph-my.sharepoint.com/personal/eloisa_baylon_deped_gov_ph/Documents/Desktop/JASON_FILE/web/ALS_PROJECT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{CDD84AC6-4E25-4955-92B4-7194A5FDD9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{7145760B-CEB7-4D3C-8B26-DFB6E1A9C246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{22E19479-EE82-45A3-9220-E5159A49DAD2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{22E19479-EE82-45A3-9220-E5159A49DAD2}"/>
   </bookViews>
   <sheets>
     <sheet name="divisions" sheetId="1" r:id="rId1"/>
     <sheet name="teachers" sheetId="2" r:id="rId2"/>
     <sheet name="schools" sheetId="3" r:id="rId3"/>
+    <sheet name="enrolment" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="463">
   <si>
     <t>id</t>
   </si>
@@ -1349,13 +1350,91 @@
   </si>
   <si>
     <t>OCAMPO, ROME NIKEY, PARAGAS</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>Basic Literacy Program</t>
+  </si>
+  <si>
+    <t>A&amp;E Elementary</t>
+  </si>
+  <si>
+    <t>A&amp;E Junior High School</t>
+  </si>
+  <si>
+    <t>BP-OSA - Mandaluyong only</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Caloocan</t>
+  </si>
+  <si>
+    <t>Las Piñas</t>
+  </si>
+  <si>
+    <t>Makati</t>
+  </si>
+  <si>
+    <t>Malabon</t>
+  </si>
+  <si>
+    <t>Mandaluyong</t>
+  </si>
+  <si>
+    <t>Manila</t>
+  </si>
+  <si>
+    <t>Marikina</t>
+  </si>
+  <si>
+    <t>Muntinlupa</t>
+  </si>
+  <si>
+    <t>Navotas</t>
+  </si>
+  <si>
+    <t>Parañaque</t>
+  </si>
+  <si>
+    <t>Pasay</t>
+  </si>
+  <si>
+    <t>Pasig</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Quezon City</t>
+  </si>
+  <si>
+    <t>San Juan</t>
+  </si>
+  <si>
+    <t>TaPat</t>
+  </si>
+  <si>
+    <t>Valenzuela</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1417,6 +1496,29 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1432,7 +1534,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1468,11 +1570,104 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1519,6 +1714,36 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7669,4 +7894,940 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90C2FF11-C04B-4FC3-A426-A14BD7863204}">
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr defaultColWidth="15.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="F1" s="22"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="I1" s="22"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="L1" s="22"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="O1" s="22"/>
+      <c r="P1" s="23"/>
+    </row>
+    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>444</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>444</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>444</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="L2" s="25" t="s">
+        <v>444</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="N2" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="O2" s="25" t="s">
+        <v>444</v>
+      </c>
+      <c r="P2" s="25" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="26" t="s">
+        <v>446</v>
+      </c>
+      <c r="B3" s="25">
+        <v>43</v>
+      </c>
+      <c r="C3" s="25">
+        <v>15</v>
+      </c>
+      <c r="D3" s="25">
+        <v>58</v>
+      </c>
+      <c r="E3" s="25">
+        <v>496</v>
+      </c>
+      <c r="F3" s="25">
+        <v>288</v>
+      </c>
+      <c r="G3" s="25">
+        <v>784</v>
+      </c>
+      <c r="H3" s="25">
+        <v>1399</v>
+      </c>
+      <c r="I3" s="25">
+        <v>1207</v>
+      </c>
+      <c r="J3" s="25">
+        <v>2606</v>
+      </c>
+      <c r="K3" s="25">
+        <v>0</v>
+      </c>
+      <c r="L3" s="25">
+        <v>0</v>
+      </c>
+      <c r="M3" s="25">
+        <v>0</v>
+      </c>
+      <c r="N3" s="25">
+        <v>1938</v>
+      </c>
+      <c r="O3" s="25">
+        <v>1510</v>
+      </c>
+      <c r="P3" s="25">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
+        <v>447</v>
+      </c>
+      <c r="B4" s="25">
+        <v>22</v>
+      </c>
+      <c r="C4" s="25">
+        <v>13</v>
+      </c>
+      <c r="D4" s="25">
+        <v>35</v>
+      </c>
+      <c r="E4" s="25">
+        <v>252</v>
+      </c>
+      <c r="F4" s="25">
+        <v>110</v>
+      </c>
+      <c r="G4" s="25">
+        <v>362</v>
+      </c>
+      <c r="H4" s="25">
+        <v>706</v>
+      </c>
+      <c r="I4" s="25">
+        <v>390</v>
+      </c>
+      <c r="J4" s="25">
+        <v>1096</v>
+      </c>
+      <c r="K4" s="25">
+        <v>0</v>
+      </c>
+      <c r="L4" s="25">
+        <v>0</v>
+      </c>
+      <c r="M4" s="25">
+        <v>0</v>
+      </c>
+      <c r="N4" s="25">
+        <v>980</v>
+      </c>
+      <c r="O4" s="25">
+        <v>513</v>
+      </c>
+      <c r="P4" s="25">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="26" t="s">
+        <v>448</v>
+      </c>
+      <c r="B5" s="25">
+        <v>27</v>
+      </c>
+      <c r="C5" s="25">
+        <v>9</v>
+      </c>
+      <c r="D5" s="25">
+        <v>36</v>
+      </c>
+      <c r="E5" s="25">
+        <v>116</v>
+      </c>
+      <c r="F5" s="25">
+        <v>182</v>
+      </c>
+      <c r="G5" s="25">
+        <v>298</v>
+      </c>
+      <c r="H5" s="25">
+        <v>249</v>
+      </c>
+      <c r="I5" s="25">
+        <v>175</v>
+      </c>
+      <c r="J5" s="25">
+        <v>424</v>
+      </c>
+      <c r="K5" s="25">
+        <v>0</v>
+      </c>
+      <c r="L5" s="25">
+        <v>0</v>
+      </c>
+      <c r="M5" s="25">
+        <v>0</v>
+      </c>
+      <c r="N5" s="25">
+        <v>392</v>
+      </c>
+      <c r="O5" s="25">
+        <v>366</v>
+      </c>
+      <c r="P5" s="25">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="26" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" s="25">
+        <v>20</v>
+      </c>
+      <c r="C6" s="25">
+        <v>9</v>
+      </c>
+      <c r="D6" s="25">
+        <v>29</v>
+      </c>
+      <c r="E6" s="25">
+        <v>97</v>
+      </c>
+      <c r="F6" s="25">
+        <v>62</v>
+      </c>
+      <c r="G6" s="25">
+        <v>159</v>
+      </c>
+      <c r="H6" s="25">
+        <v>185</v>
+      </c>
+      <c r="I6" s="25">
+        <v>168</v>
+      </c>
+      <c r="J6" s="25">
+        <v>353</v>
+      </c>
+      <c r="K6" s="25">
+        <v>0</v>
+      </c>
+      <c r="L6" s="25">
+        <v>0</v>
+      </c>
+      <c r="M6" s="25">
+        <v>0</v>
+      </c>
+      <c r="N6" s="25">
+        <v>302</v>
+      </c>
+      <c r="O6" s="25">
+        <v>239</v>
+      </c>
+      <c r="P6" s="25">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="26" t="s">
+        <v>450</v>
+      </c>
+      <c r="B7" s="25">
+        <v>20</v>
+      </c>
+      <c r="C7" s="25">
+        <v>45</v>
+      </c>
+      <c r="D7" s="25">
+        <v>65</v>
+      </c>
+      <c r="E7" s="25">
+        <v>139</v>
+      </c>
+      <c r="F7" s="25">
+        <v>83</v>
+      </c>
+      <c r="G7" s="25">
+        <v>222</v>
+      </c>
+      <c r="H7" s="25">
+        <v>525</v>
+      </c>
+      <c r="I7" s="25">
+        <v>384</v>
+      </c>
+      <c r="J7" s="25">
+        <v>909</v>
+      </c>
+      <c r="K7" s="25">
+        <v>143</v>
+      </c>
+      <c r="L7" s="25">
+        <v>91</v>
+      </c>
+      <c r="M7" s="25">
+        <v>234</v>
+      </c>
+      <c r="N7" s="25">
+        <v>827</v>
+      </c>
+      <c r="O7" s="25">
+        <v>603</v>
+      </c>
+      <c r="P7" s="25">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="B8" s="25">
+        <v>71</v>
+      </c>
+      <c r="C8" s="25">
+        <v>63</v>
+      </c>
+      <c r="D8" s="25">
+        <v>134</v>
+      </c>
+      <c r="E8" s="25">
+        <v>1358</v>
+      </c>
+      <c r="F8" s="25">
+        <v>872</v>
+      </c>
+      <c r="G8" s="25">
+        <v>2230</v>
+      </c>
+      <c r="H8" s="25">
+        <v>2470</v>
+      </c>
+      <c r="I8" s="25">
+        <v>1862</v>
+      </c>
+      <c r="J8" s="25">
+        <v>4332</v>
+      </c>
+      <c r="K8" s="25">
+        <v>0</v>
+      </c>
+      <c r="L8" s="25">
+        <v>0</v>
+      </c>
+      <c r="M8" s="25">
+        <v>0</v>
+      </c>
+      <c r="N8" s="25">
+        <v>3899</v>
+      </c>
+      <c r="O8" s="25">
+        <v>2797</v>
+      </c>
+      <c r="P8" s="25">
+        <v>6696</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="26" t="s">
+        <v>452</v>
+      </c>
+      <c r="B9" s="25">
+        <v>2</v>
+      </c>
+      <c r="C9" s="25">
+        <v>2</v>
+      </c>
+      <c r="D9" s="25">
+        <v>4</v>
+      </c>
+      <c r="E9" s="25">
+        <v>99</v>
+      </c>
+      <c r="F9" s="25">
+        <v>63</v>
+      </c>
+      <c r="G9" s="25">
+        <v>162</v>
+      </c>
+      <c r="H9" s="25">
+        <v>330</v>
+      </c>
+      <c r="I9" s="25">
+        <v>232</v>
+      </c>
+      <c r="J9" s="25">
+        <v>562</v>
+      </c>
+      <c r="K9" s="25">
+        <v>0</v>
+      </c>
+      <c r="L9" s="25">
+        <v>0</v>
+      </c>
+      <c r="M9" s="25">
+        <v>0</v>
+      </c>
+      <c r="N9" s="25">
+        <v>431</v>
+      </c>
+      <c r="O9" s="25">
+        <v>297</v>
+      </c>
+      <c r="P9" s="25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="26" t="s">
+        <v>453</v>
+      </c>
+      <c r="B10" s="25">
+        <v>282</v>
+      </c>
+      <c r="C10" s="25">
+        <v>10</v>
+      </c>
+      <c r="D10" s="25">
+        <v>292</v>
+      </c>
+      <c r="E10" s="25">
+        <v>793</v>
+      </c>
+      <c r="F10" s="25">
+        <v>90</v>
+      </c>
+      <c r="G10" s="25">
+        <v>883</v>
+      </c>
+      <c r="H10" s="25">
+        <v>1331</v>
+      </c>
+      <c r="I10" s="25">
+        <v>384</v>
+      </c>
+      <c r="J10" s="25">
+        <v>1715</v>
+      </c>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="25">
+        <v>0</v>
+      </c>
+      <c r="N10" s="25">
+        <v>2406</v>
+      </c>
+      <c r="O10" s="25">
+        <v>484</v>
+      </c>
+      <c r="P10" s="25">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="26" t="s">
+        <v>454</v>
+      </c>
+      <c r="B11" s="25">
+        <v>37</v>
+      </c>
+      <c r="C11" s="25">
+        <v>12</v>
+      </c>
+      <c r="D11" s="25">
+        <v>49</v>
+      </c>
+      <c r="E11" s="25">
+        <v>134</v>
+      </c>
+      <c r="F11" s="25">
+        <v>79</v>
+      </c>
+      <c r="G11" s="25">
+        <v>213</v>
+      </c>
+      <c r="H11" s="25">
+        <v>249</v>
+      </c>
+      <c r="I11" s="25">
+        <v>214</v>
+      </c>
+      <c r="J11" s="25">
+        <v>463</v>
+      </c>
+      <c r="K11" s="25">
+        <v>0</v>
+      </c>
+      <c r="L11" s="25">
+        <v>0</v>
+      </c>
+      <c r="M11" s="25">
+        <v>0</v>
+      </c>
+      <c r="N11" s="25">
+        <v>420</v>
+      </c>
+      <c r="O11" s="25">
+        <v>305</v>
+      </c>
+      <c r="P11" s="25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="26" t="s">
+        <v>455</v>
+      </c>
+      <c r="B12" s="25">
+        <v>14</v>
+      </c>
+      <c r="C12" s="25">
+        <v>11</v>
+      </c>
+      <c r="D12" s="25">
+        <v>25</v>
+      </c>
+      <c r="E12" s="25">
+        <v>163</v>
+      </c>
+      <c r="F12" s="25">
+        <v>130</v>
+      </c>
+      <c r="G12" s="25">
+        <v>293</v>
+      </c>
+      <c r="H12" s="25">
+        <v>463</v>
+      </c>
+      <c r="I12" s="25">
+        <v>493</v>
+      </c>
+      <c r="J12" s="25">
+        <v>956</v>
+      </c>
+      <c r="K12" s="25">
+        <v>0</v>
+      </c>
+      <c r="L12" s="25">
+        <v>0</v>
+      </c>
+      <c r="M12" s="25">
+        <v>0</v>
+      </c>
+      <c r="N12" s="25">
+        <v>640</v>
+      </c>
+      <c r="O12" s="25">
+        <v>634</v>
+      </c>
+      <c r="P12" s="25">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="26" t="s">
+        <v>456</v>
+      </c>
+      <c r="B13" s="25">
+        <v>85</v>
+      </c>
+      <c r="C13" s="25">
+        <v>24</v>
+      </c>
+      <c r="D13" s="25">
+        <v>109</v>
+      </c>
+      <c r="E13" s="25">
+        <v>185</v>
+      </c>
+      <c r="F13" s="25">
+        <v>130</v>
+      </c>
+      <c r="G13" s="25">
+        <v>315</v>
+      </c>
+      <c r="H13" s="25">
+        <v>528</v>
+      </c>
+      <c r="I13" s="25">
+        <v>629</v>
+      </c>
+      <c r="J13" s="25">
+        <v>1157</v>
+      </c>
+      <c r="K13" s="25">
+        <v>0</v>
+      </c>
+      <c r="L13" s="25">
+        <v>0</v>
+      </c>
+      <c r="M13" s="25">
+        <v>0</v>
+      </c>
+      <c r="N13" s="25">
+        <v>798</v>
+      </c>
+      <c r="O13" s="25">
+        <v>783</v>
+      </c>
+      <c r="P13" s="25">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="26" t="s">
+        <v>457</v>
+      </c>
+      <c r="B14" s="25">
+        <v>15</v>
+      </c>
+      <c r="C14" s="25">
+        <v>11</v>
+      </c>
+      <c r="D14" s="25">
+        <v>26</v>
+      </c>
+      <c r="E14" s="25">
+        <v>146</v>
+      </c>
+      <c r="F14" s="25">
+        <v>64</v>
+      </c>
+      <c r="G14" s="25">
+        <v>210</v>
+      </c>
+      <c r="H14" s="25">
+        <v>687</v>
+      </c>
+      <c r="I14" s="25">
+        <v>436</v>
+      </c>
+      <c r="J14" s="25">
+        <v>1123</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="L14" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="M14" s="25">
+        <v>0</v>
+      </c>
+      <c r="N14" s="25">
+        <v>848</v>
+      </c>
+      <c r="O14" s="25">
+        <v>511</v>
+      </c>
+      <c r="P14" s="25">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="26" t="s">
+        <v>459</v>
+      </c>
+      <c r="B15" s="25">
+        <v>74</v>
+      </c>
+      <c r="C15" s="25">
+        <v>36</v>
+      </c>
+      <c r="D15" s="25">
+        <v>110</v>
+      </c>
+      <c r="E15" s="25">
+        <v>527</v>
+      </c>
+      <c r="F15" s="25">
+        <v>260</v>
+      </c>
+      <c r="G15" s="25">
+        <v>787</v>
+      </c>
+      <c r="H15" s="25">
+        <v>1782</v>
+      </c>
+      <c r="I15" s="25">
+        <v>1240</v>
+      </c>
+      <c r="J15" s="25">
+        <v>3022</v>
+      </c>
+      <c r="K15" s="25">
+        <v>0</v>
+      </c>
+      <c r="L15" s="25">
+        <v>0</v>
+      </c>
+      <c r="M15" s="25">
+        <v>0</v>
+      </c>
+      <c r="N15" s="25">
+        <v>2383</v>
+      </c>
+      <c r="O15" s="25">
+        <v>1536</v>
+      </c>
+      <c r="P15" s="25">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="26" t="s">
+        <v>460</v>
+      </c>
+      <c r="B16" s="25">
+        <v>4</v>
+      </c>
+      <c r="C16" s="25">
+        <v>6</v>
+      </c>
+      <c r="D16" s="25">
+        <v>10</v>
+      </c>
+      <c r="E16" s="25">
+        <v>28</v>
+      </c>
+      <c r="F16" s="25">
+        <v>19</v>
+      </c>
+      <c r="G16" s="25">
+        <v>47</v>
+      </c>
+      <c r="H16" s="25">
+        <v>100</v>
+      </c>
+      <c r="I16" s="25">
+        <v>69</v>
+      </c>
+      <c r="J16" s="25">
+        <v>169</v>
+      </c>
+      <c r="K16" s="25">
+        <v>0</v>
+      </c>
+      <c r="L16" s="25">
+        <v>0</v>
+      </c>
+      <c r="M16" s="25">
+        <v>0</v>
+      </c>
+      <c r="N16" s="25">
+        <v>132</v>
+      </c>
+      <c r="O16" s="25">
+        <v>94</v>
+      </c>
+      <c r="P16" s="25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="26" t="s">
+        <v>461</v>
+      </c>
+      <c r="B17" s="25">
+        <v>30</v>
+      </c>
+      <c r="C17" s="25">
+        <v>22</v>
+      </c>
+      <c r="D17" s="25">
+        <v>52</v>
+      </c>
+      <c r="E17" s="25">
+        <v>393</v>
+      </c>
+      <c r="F17" s="25">
+        <v>209</v>
+      </c>
+      <c r="G17" s="25">
+        <v>602</v>
+      </c>
+      <c r="H17" s="25">
+        <v>1269</v>
+      </c>
+      <c r="I17" s="25">
+        <v>898</v>
+      </c>
+      <c r="J17" s="25">
+        <v>2167</v>
+      </c>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="25">
+        <v>0</v>
+      </c>
+      <c r="N17" s="25">
+        <v>1692</v>
+      </c>
+      <c r="O17" s="25">
+        <v>1129</v>
+      </c>
+      <c r="P17" s="25">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="26" t="s">
+        <v>462</v>
+      </c>
+      <c r="B18" s="25">
+        <v>20</v>
+      </c>
+      <c r="C18" s="25">
+        <v>15</v>
+      </c>
+      <c r="D18" s="25">
+        <v>35</v>
+      </c>
+      <c r="E18" s="25">
+        <v>110</v>
+      </c>
+      <c r="F18" s="25">
+        <v>65</v>
+      </c>
+      <c r="G18" s="25">
+        <v>175</v>
+      </c>
+      <c r="H18" s="25">
+        <v>466</v>
+      </c>
+      <c r="I18" s="25">
+        <v>284</v>
+      </c>
+      <c r="J18" s="25">
+        <v>750</v>
+      </c>
+      <c r="K18" s="25">
+        <v>0</v>
+      </c>
+      <c r="L18" s="25">
+        <v>0</v>
+      </c>
+      <c r="M18" s="25">
+        <v>0</v>
+      </c>
+      <c r="N18" s="25">
+        <v>596</v>
+      </c>
+      <c r="O18" s="25">
+        <v>364</v>
+      </c>
+      <c r="P18" s="25">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29">
+        <v>766</v>
+      </c>
+      <c r="C19" s="29">
+        <v>303</v>
+      </c>
+      <c r="D19" s="29">
+        <v>1069</v>
+      </c>
+      <c r="E19" s="29">
+        <v>5036</v>
+      </c>
+      <c r="F19" s="29">
+        <v>2706</v>
+      </c>
+      <c r="G19" s="29">
+        <v>7742</v>
+      </c>
+      <c r="H19" s="29">
+        <v>12739</v>
+      </c>
+      <c r="I19" s="29">
+        <v>9065</v>
+      </c>
+      <c r="J19" s="29">
+        <v>21804</v>
+      </c>
+      <c r="K19" s="29">
+        <v>143</v>
+      </c>
+      <c r="L19" s="29">
+        <v>91</v>
+      </c>
+      <c r="M19" s="29">
+        <v>234</v>
+      </c>
+      <c r="N19" s="29">
+        <v>18684</v>
+      </c>
+      <c r="O19" s="29">
+        <v>12165</v>
+      </c>
+      <c r="P19" s="29">
+        <v>30849</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://depedph-my.sharepoint.com/personal/eloisa_baylon_deped_gov_ph/Documents/Desktop/JASON_FILE/web/ALS_PROJECT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{7145760B-CEB7-4D3C-8B26-DFB6E1A9C246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{F8F2432F-C2F2-4C2B-9E21-384769B1DA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{22E19479-EE82-45A3-9220-E5159A49DAD2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{22E19479-EE82-45A3-9220-E5159A49DAD2}"/>
   </bookViews>
   <sheets>
     <sheet name="divisions" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="schools" sheetId="3" r:id="rId3"/>
     <sheet name="enrolment" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">teachers!$A$1:$D$389</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="461">
   <si>
     <t>id</t>
   </si>
@@ -311,9 +314,6 @@
     <t>Teacher</t>
   </si>
   <si>
-    <t>Teacher 1</t>
-  </si>
-  <si>
     <t>ARGOTE, CHRISTINE MAY, DAIRO</t>
   </si>
   <si>
@@ -399,9 +399,6 @@
   </si>
   <si>
     <t>TUMALIUAN, JESUSA, ABAN</t>
-  </si>
-  <si>
-    <t>teacher III</t>
   </si>
   <si>
     <t>ARELLANO, KIMBERLY, PALER</t>
@@ -1434,7 +1431,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1463,18 +1460,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF434343"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1518,6 +1503,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1679,70 +1670,68 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2229,6 +2218,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD847B43-07E4-4458-A0B5-A7B3D7D8E6F7}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D389"/>
   <sheetFormatPr defaultColWidth="5.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2263,7 +2253,7 @@
       <c r="C2" s="5">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2272,26 +2262,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C3" s="5">
         <v>1</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D3" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C4" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2305,7 +2295,7 @@
       <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2319,7 +2309,7 @@
       <c r="C6" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2333,7 +2323,7 @@
       <c r="C7" s="5">
         <v>1</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2347,7 +2337,7 @@
       <c r="C8" s="5">
         <v>1</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2361,7 +2351,7 @@
       <c r="C9" s="5">
         <v>1</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2370,12 +2360,12 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2389,7 +2379,7 @@
       <c r="C11" s="5">
         <v>1</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2403,7 +2393,7 @@
       <c r="C12" s="5">
         <v>1</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2417,7 +2407,7 @@
       <c r="C13" s="5">
         <v>1</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2431,11 +2421,11 @@
       <c r="C14" s="5">
         <v>1</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D14" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -2445,7 +2435,7 @@
       <c r="C15" s="5">
         <v>1</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2459,7 +2449,7 @@
       <c r="C16" s="5">
         <v>1</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2473,7 +2463,7 @@
       <c r="C17" s="5">
         <v>1</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2487,7 +2477,7 @@
       <c r="C18" s="5">
         <v>1</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2501,7 +2491,7 @@
       <c r="C19" s="5">
         <v>1</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2509,27 +2499,27 @@
       <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="5">
         <v>1</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D20" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C21" s="5">
         <v>1</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2543,7 +2533,7 @@
       <c r="C22" s="5">
         <v>1</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2557,7 +2547,7 @@
       <c r="C23" s="5">
         <v>1</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2566,12 +2556,12 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2585,33 +2575,33 @@
       <c r="C25" s="5">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D25" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C26" s="5">
         <v>2</v>
       </c>
-      <c r="D26" s="10"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D26" s="21"/>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C27" s="5">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2625,7 +2615,7 @@
       <c r="C28" s="5">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2639,7 +2629,7 @@
       <c r="C29" s="5">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2653,7 +2643,7 @@
       <c r="C30" s="5">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2662,16 +2652,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C31" s="5">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D31" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -2681,21 +2671,21 @@
       <c r="C32" s="5">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C33" s="5">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2709,7 +2699,7 @@
       <c r="C34" s="5">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2718,26 +2708,26 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C35" s="5">
         <v>2</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C36" s="5">
         <v>2</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2751,7 +2741,7 @@
       <c r="C37" s="5">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2765,11 +2755,11 @@
       <c r="C38" s="5">
         <v>2</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -2779,7 +2769,7 @@
       <c r="C39" s="5">
         <v>2</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2788,54 +2778,54 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C40" s="5">
         <v>3</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C41" s="5">
         <v>3</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C42" s="5">
         <v>3</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C43" s="5">
         <v>3</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2844,12 +2834,12 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C44" s="5">
         <v>3</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2858,12 +2848,12 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C45" s="5">
         <v>4</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2877,7 +2867,7 @@
       <c r="C46" s="5">
         <v>4</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2891,21 +2881,21 @@
       <c r="C47" s="5">
         <v>4</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D47" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C48" s="5">
         <v>4</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2914,68 +2904,68 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C49" s="5">
         <v>4</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D49" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C50" s="5">
         <v>4</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C51" s="5">
         <v>4</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C52" s="5">
         <v>4</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C53" s="5">
         <v>4</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2983,27 +2973,27 @@
       <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C54" s="5">
         <v>4</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D54" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C55" s="5">
         <v>5</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3012,12 +3002,12 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C56" s="5">
         <v>5</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3031,7 +3021,7 @@
       <c r="C57" s="5">
         <v>5</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3045,53 +3035,53 @@
       <c r="C58" s="5">
         <v>5</v>
       </c>
-      <c r="D58" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D58" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C59" s="5">
         <v>5</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C60" s="5">
         <v>5</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C61" s="5">
         <v>5</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -3101,141 +3091,141 @@
       <c r="C62" s="5">
         <v>5</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>190</v>
+      <c r="B63" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="C63" s="5">
         <v>6</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="9" t="s">
-        <v>191</v>
+      <c r="B64" s="8" t="s">
+        <v>189</v>
       </c>
       <c r="C64" s="5">
         <v>6</v>
       </c>
-      <c r="D64" s="13"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D64" s="22"/>
+    </row>
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="9" t="s">
-        <v>192</v>
+      <c r="B65" s="8" t="s">
+        <v>190</v>
       </c>
       <c r="C65" s="5">
         <v>6</v>
       </c>
-      <c r="D65" s="13"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D65" s="22"/>
+    </row>
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>200</v>
+      <c r="B66" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="C66" s="5">
         <v>6</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C67" s="5">
         <v>6</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>67</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="8" t="s">
         <v>80</v>
       </c>
       <c r="C68" s="5">
         <v>6</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>68</v>
       </c>
-      <c r="B69" s="9" t="s">
-        <v>201</v>
+      <c r="B69" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="C69" s="5">
         <v>6</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="9" t="s">
-        <v>202</v>
+      <c r="B70" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="C70" s="5">
         <v>6</v>
       </c>
-      <c r="D70" s="13"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D70" s="22"/>
+    </row>
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>203</v>
+      <c r="B71" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="C71" s="5">
         <v>6</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="9" t="s">
-        <v>204</v>
+      <c r="B72" s="8" t="s">
+        <v>202</v>
       </c>
       <c r="C72" s="5">
         <v>6</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3243,97 +3233,97 @@
       <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="9" t="s">
-        <v>205</v>
+      <c r="B73" s="8" t="s">
+        <v>203</v>
       </c>
       <c r="C73" s="5">
         <v>6</v>
       </c>
-      <c r="D73" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D73" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="8" t="s">
         <v>81</v>
       </c>
       <c r="C74" s="5">
         <v>6</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="9" t="s">
-        <v>206</v>
+      <c r="B75" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="C75" s="5">
         <v>6</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C76" s="5">
         <v>6</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="9" t="s">
-        <v>207</v>
+      <c r="B77" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="C77" s="5">
         <v>6</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="9" t="s">
-        <v>208</v>
+      <c r="B78" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="C78" s="5">
         <v>6</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="9" t="s">
-        <v>209</v>
+      <c r="B79" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="C79" s="5">
         <v>6</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3341,69 +3331,69 @@
       <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>210</v>
+      <c r="B80" s="8" t="s">
+        <v>208</v>
       </c>
       <c r="C80" s="5">
         <v>6</v>
       </c>
-      <c r="D80" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D80" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>211</v>
+      <c r="B81" s="8" t="s">
+        <v>209</v>
       </c>
       <c r="C81" s="5">
         <v>6</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>81</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>212</v>
+      <c r="B82" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="C82" s="5">
         <v>6</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="9" t="s">
-        <v>213</v>
+      <c r="B83" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="C83" s="5">
         <v>6</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>83</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>214</v>
+      <c r="B84" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="C84" s="5">
         <v>6</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3411,27 +3401,27 @@
       <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="9" t="s">
-        <v>215</v>
+      <c r="B85" s="8" t="s">
+        <v>213</v>
       </c>
       <c r="C85" s="5">
         <v>6</v>
       </c>
-      <c r="D85" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D85" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>85</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>216</v>
+      <c r="B86" s="8" t="s">
+        <v>214</v>
       </c>
       <c r="C86" s="5">
         <v>6</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3439,13 +3429,13 @@
       <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="9" t="s">
-        <v>217</v>
+      <c r="B87" s="8" t="s">
+        <v>215</v>
       </c>
       <c r="C87" s="5">
         <v>6</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3453,41 +3443,41 @@
       <c r="A88" s="5">
         <v>87</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>218</v>
+      <c r="B88" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="C88" s="5">
         <v>6</v>
       </c>
-      <c r="D88" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D88" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>88</v>
       </c>
-      <c r="B89" s="9" t="s">
-        <v>208</v>
+      <c r="B89" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="C89" s="5">
         <v>6</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>89</v>
       </c>
-      <c r="B90" s="9" t="s">
-        <v>219</v>
+      <c r="B90" s="8" t="s">
+        <v>217</v>
       </c>
       <c r="C90" s="5">
         <v>6</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3495,13 +3485,13 @@
       <c r="A91" s="5">
         <v>90</v>
       </c>
-      <c r="B91" s="9" t="s">
-        <v>220</v>
+      <c r="B91" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="C91" s="5">
         <v>6</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3509,55 +3499,55 @@
       <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="9" t="s">
-        <v>221</v>
+      <c r="B92" s="8" t="s">
+        <v>219</v>
       </c>
       <c r="C92" s="5">
         <v>6</v>
       </c>
-      <c r="D92" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D92" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="9" t="s">
-        <v>222</v>
+      <c r="B93" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="C93" s="5">
         <v>6</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>93</v>
       </c>
-      <c r="B94" s="9" t="s">
-        <v>223</v>
+      <c r="B94" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="C94" s="5">
         <v>6</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="B95" s="9" t="s">
-        <v>224</v>
+      <c r="B95" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="C95" s="5">
         <v>6</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3565,13 +3555,13 @@
       <c r="A96" s="5">
         <v>95</v>
       </c>
-      <c r="B96" s="9" t="s">
-        <v>225</v>
+      <c r="B96" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="C96" s="5">
         <v>6</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3579,13 +3569,13 @@
       <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="9" t="s">
-        <v>226</v>
+      <c r="B97" s="8" t="s">
+        <v>224</v>
       </c>
       <c r="C97" s="5">
         <v>6</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3593,13 +3583,13 @@
       <c r="A98" s="5">
         <v>97</v>
       </c>
-      <c r="B98" s="9" t="s">
-        <v>227</v>
+      <c r="B98" s="8" t="s">
+        <v>225</v>
       </c>
       <c r="C98" s="5">
         <v>6</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3607,55 +3597,55 @@
       <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="9" t="s">
-        <v>228</v>
+      <c r="B99" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="C99" s="5">
         <v>6</v>
       </c>
-      <c r="D99" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D99" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="9" t="s">
-        <v>229</v>
+      <c r="B100" s="8" t="s">
+        <v>227</v>
       </c>
       <c r="C100" s="5">
         <v>6</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="D100" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="9" t="s">
-        <v>230</v>
+      <c r="B101" s="8" t="s">
+        <v>228</v>
       </c>
       <c r="C101" s="5">
         <v>6</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>101</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="8" t="s">
         <v>83</v>
       </c>
       <c r="C102" s="5">
         <v>6</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3663,13 +3653,13 @@
       <c r="A103" s="5">
         <v>102</v>
       </c>
-      <c r="B103" s="9" t="s">
-        <v>231</v>
+      <c r="B103" s="8" t="s">
+        <v>229</v>
       </c>
       <c r="C103" s="5">
         <v>6</v>
       </c>
-      <c r="D103" s="12" t="s">
+      <c r="D103" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3677,39 +3667,39 @@
       <c r="A104" s="5">
         <v>103</v>
       </c>
-      <c r="B104" s="9" t="s">
-        <v>232</v>
+      <c r="B104" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="C104" s="5">
         <v>6</v>
       </c>
-      <c r="D104" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D104" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="B105" s="9" t="s">
-        <v>233</v>
+      <c r="B105" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="C105" s="5">
         <v>6</v>
       </c>
-      <c r="D105" s="13"/>
+      <c r="D105" s="22"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>105</v>
       </c>
-      <c r="B106" s="9" t="s">
-        <v>234</v>
+      <c r="B106" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="C106" s="5">
         <v>6</v>
       </c>
-      <c r="D106" s="12" t="s">
+      <c r="D106" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3717,41 +3707,41 @@
       <c r="A107" s="5">
         <v>106</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" s="8" t="s">
         <v>84</v>
       </c>
       <c r="C107" s="5">
         <v>6</v>
       </c>
-      <c r="D107" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D107" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>107</v>
       </c>
-      <c r="B108" s="9" t="s">
-        <v>235</v>
+      <c r="B108" s="8" t="s">
+        <v>233</v>
       </c>
       <c r="C108" s="5">
         <v>6</v>
       </c>
-      <c r="D108" s="12" t="s">
+      <c r="D108" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>108</v>
       </c>
-      <c r="B109" s="9" t="s">
-        <v>236</v>
+      <c r="B109" s="8" t="s">
+        <v>234</v>
       </c>
       <c r="C109" s="5">
         <v>6</v>
       </c>
-      <c r="D109" s="12" t="s">
+      <c r="D109" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3759,53 +3749,53 @@
       <c r="A110" s="5">
         <v>109</v>
       </c>
-      <c r="B110" s="9" t="s">
-        <v>237</v>
+      <c r="B110" s="8" t="s">
+        <v>235</v>
       </c>
       <c r="C110" s="5">
         <v>6</v>
       </c>
-      <c r="D110" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D110" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>110</v>
       </c>
-      <c r="B111" s="9" t="s">
-        <v>238</v>
+      <c r="B111" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="C111" s="5">
         <v>6</v>
       </c>
-      <c r="D111" s="13"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D111" s="22"/>
+    </row>
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>111</v>
       </c>
-      <c r="B112" s="9" t="s">
-        <v>239</v>
+      <c r="B112" s="8" t="s">
+        <v>237</v>
       </c>
       <c r="C112" s="5">
         <v>6</v>
       </c>
-      <c r="D112" s="12" t="s">
+      <c r="D112" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>112</v>
       </c>
-      <c r="B113" s="9" t="s">
-        <v>240</v>
+      <c r="B113" s="8" t="s">
+        <v>238</v>
       </c>
       <c r="C113" s="5">
         <v>6</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D113" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3813,205 +3803,205 @@
       <c r="A114" s="5">
         <v>113</v>
       </c>
-      <c r="B114" s="9" t="s">
-        <v>241</v>
+      <c r="B114" s="8" t="s">
+        <v>239</v>
       </c>
       <c r="C114" s="5">
         <v>6</v>
       </c>
-      <c r="D114" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D114" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>114</v>
       </c>
-      <c r="B115" s="9" t="s">
-        <v>242</v>
+      <c r="B115" s="8" t="s">
+        <v>240</v>
       </c>
       <c r="C115" s="5">
         <v>6</v>
       </c>
-      <c r="D115" s="13"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D115" s="22"/>
+    </row>
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>115</v>
       </c>
-      <c r="B116" s="9" t="s">
+      <c r="B116" s="8" t="s">
         <v>85</v>
       </c>
       <c r="C116" s="5">
         <v>6</v>
       </c>
-      <c r="D116" s="12" t="s">
+      <c r="D116" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>116</v>
       </c>
-      <c r="B117" s="9" t="s">
-        <v>243</v>
+      <c r="B117" s="8" t="s">
+        <v>241</v>
       </c>
       <c r="C117" s="5">
         <v>6</v>
       </c>
-      <c r="D117" s="12" t="s">
+      <c r="D117" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>117</v>
       </c>
-      <c r="B118" s="9" t="s">
-        <v>244</v>
+      <c r="B118" s="8" t="s">
+        <v>242</v>
       </c>
       <c r="C118" s="5">
         <v>6</v>
       </c>
-      <c r="D118" s="12" t="s">
+      <c r="D118" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>118</v>
       </c>
-      <c r="B119" s="9" t="s">
-        <v>245</v>
+      <c r="B119" s="8" t="s">
+        <v>243</v>
       </c>
       <c r="C119" s="5">
         <v>6</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="D119" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>119</v>
       </c>
-      <c r="B120" s="9" t="s">
-        <v>246</v>
+      <c r="B120" s="8" t="s">
+        <v>244</v>
       </c>
       <c r="C120" s="5">
         <v>6</v>
       </c>
-      <c r="D120" s="13"/>
+      <c r="D120" s="22"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>120</v>
       </c>
-      <c r="B121" s="9" t="s">
-        <v>247</v>
+      <c r="B121" s="8" t="s">
+        <v>245</v>
       </c>
       <c r="C121" s="5">
         <v>6</v>
       </c>
-      <c r="D121" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D121" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>121</v>
       </c>
-      <c r="B122" s="9" t="s">
-        <v>248</v>
+      <c r="B122" s="8" t="s">
+        <v>246</v>
       </c>
       <c r="C122" s="5">
         <v>6</v>
       </c>
-      <c r="D122" s="12" t="s">
+      <c r="D122" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>122</v>
       </c>
-      <c r="B123" s="9" t="s">
-        <v>249</v>
+      <c r="B123" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="C123" s="5">
         <v>6</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>123</v>
       </c>
-      <c r="B124" s="9" t="s">
-        <v>250</v>
+      <c r="B124" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="C124" s="5">
         <v>6</v>
       </c>
-      <c r="D124" s="12" t="s">
+      <c r="D124" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>124</v>
       </c>
-      <c r="B125" s="9" t="s">
-        <v>251</v>
+      <c r="B125" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="C125" s="5">
         <v>6</v>
       </c>
-      <c r="D125" s="12" t="s">
+      <c r="D125" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>125</v>
       </c>
-      <c r="B126" s="9" t="s">
-        <v>252</v>
+      <c r="B126" s="8" t="s">
+        <v>250</v>
       </c>
       <c r="C126" s="5">
         <v>6</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>126</v>
       </c>
-      <c r="B127" s="9" t="s">
-        <v>253</v>
+      <c r="B127" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="C127" s="5">
         <v>6</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>127</v>
       </c>
-      <c r="B128" s="9" t="s">
-        <v>254</v>
+      <c r="B128" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="C128" s="5">
         <v>6</v>
       </c>
-      <c r="D128" s="12" t="s">
+      <c r="D128" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4019,27 +4009,27 @@
       <c r="A129" s="5">
         <v>128</v>
       </c>
-      <c r="B129" s="9" t="s">
-        <v>255</v>
+      <c r="B129" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="C129" s="5">
         <v>6</v>
       </c>
-      <c r="D129" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D129" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>129</v>
       </c>
-      <c r="B130" s="9" t="s">
-        <v>256</v>
+      <c r="B130" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="C130" s="5">
         <v>6</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D130" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4047,13 +4037,13 @@
       <c r="A131" s="5">
         <v>130</v>
       </c>
-      <c r="B131" s="9" t="s">
-        <v>257</v>
+      <c r="B131" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="C131" s="5">
         <v>6</v>
       </c>
-      <c r="D131" s="12" t="s">
+      <c r="D131" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4061,145 +4051,145 @@
       <c r="A132" s="5">
         <v>131</v>
       </c>
-      <c r="B132" s="9" t="s">
-        <v>258</v>
+      <c r="B132" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="C132" s="5">
         <v>6</v>
       </c>
-      <c r="D132" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D132" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>132</v>
       </c>
-      <c r="B133" s="9" t="s">
-        <v>259</v>
+      <c r="B133" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="C133" s="5">
         <v>6</v>
       </c>
-      <c r="D133" s="13"/>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D133" s="22"/>
+    </row>
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>133</v>
       </c>
-      <c r="B134" s="9" t="s">
-        <v>260</v>
+      <c r="B134" s="8" t="s">
+        <v>258</v>
       </c>
       <c r="C134" s="5">
         <v>6</v>
       </c>
-      <c r="D134" s="13"/>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D134" s="22"/>
+    </row>
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>134</v>
       </c>
-      <c r="B135" s="9" t="s">
-        <v>261</v>
+      <c r="B135" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="C135" s="5">
         <v>6</v>
       </c>
-      <c r="D135" s="12" t="s">
+      <c r="D135" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>135</v>
       </c>
-      <c r="B136" s="9" t="s">
-        <v>262</v>
+      <c r="B136" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="C136" s="5">
         <v>6</v>
       </c>
-      <c r="D136" s="12" t="s">
+      <c r="D136" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>136</v>
       </c>
-      <c r="B137" s="9" t="s">
-        <v>263</v>
+      <c r="B137" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="C137" s="5">
         <v>6</v>
       </c>
-      <c r="D137" s="13"/>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D137" s="22"/>
+    </row>
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>137</v>
       </c>
-      <c r="B138" s="9" t="s">
-        <v>264</v>
+      <c r="B138" s="8" t="s">
+        <v>262</v>
       </c>
       <c r="C138" s="5">
         <v>6</v>
       </c>
-      <c r="D138" s="12" t="s">
+      <c r="D138" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>138</v>
       </c>
-      <c r="B139" s="9" t="s">
-        <v>265</v>
+      <c r="B139" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="C139" s="5">
         <v>6</v>
       </c>
-      <c r="D139" s="13"/>
+      <c r="D139" s="22"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>139</v>
       </c>
-      <c r="B140" s="9" t="s">
-        <v>266</v>
+      <c r="B140" s="8" t="s">
+        <v>264</v>
       </c>
       <c r="C140" s="5">
         <v>6</v>
       </c>
-      <c r="D140" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D140" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>140</v>
       </c>
-      <c r="B141" s="9" t="s">
-        <v>267</v>
+      <c r="B141" s="8" t="s">
+        <v>265</v>
       </c>
       <c r="C141" s="5">
         <v>6</v>
       </c>
-      <c r="D141" s="12" t="s">
+      <c r="D141" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>141</v>
       </c>
-      <c r="B142" s="9" t="s">
-        <v>268</v>
+      <c r="B142" s="8" t="s">
+        <v>266</v>
       </c>
       <c r="C142" s="5">
         <v>6</v>
       </c>
-      <c r="D142" s="12" t="s">
+      <c r="D142" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4207,95 +4197,95 @@
       <c r="A143" s="5">
         <v>142</v>
       </c>
-      <c r="B143" s="9" t="s">
-        <v>269</v>
+      <c r="B143" s="8" t="s">
+        <v>267</v>
       </c>
       <c r="C143" s="5">
         <v>6</v>
       </c>
-      <c r="D143" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D143" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>143</v>
       </c>
-      <c r="B144" s="9" t="s">
-        <v>270</v>
+      <c r="B144" s="8" t="s">
+        <v>268</v>
       </c>
       <c r="C144" s="5">
         <v>6</v>
       </c>
-      <c r="D144" s="12" t="s">
+      <c r="D144" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>144</v>
       </c>
-      <c r="B145" s="9" t="s">
-        <v>271</v>
+      <c r="B145" s="8" t="s">
+        <v>269</v>
       </c>
       <c r="C145" s="5">
         <v>6</v>
       </c>
-      <c r="D145" s="12" t="s">
+      <c r="D145" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>145</v>
       </c>
-      <c r="B146" s="9" t="s">
-        <v>272</v>
+      <c r="B146" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="C146" s="5">
         <v>6</v>
       </c>
-      <c r="D146" s="13"/>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D146" s="22"/>
+    </row>
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>146</v>
       </c>
-      <c r="B147" s="9" t="s">
-        <v>273</v>
+      <c r="B147" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="C147" s="5">
         <v>6</v>
       </c>
-      <c r="D147" s="12" t="s">
+      <c r="D147" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>147</v>
       </c>
-      <c r="B148" s="9" t="s">
-        <v>274</v>
+      <c r="B148" s="8" t="s">
+        <v>272</v>
       </c>
       <c r="C148" s="5">
         <v>6</v>
       </c>
-      <c r="D148" s="12" t="s">
+      <c r="D148" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>148</v>
       </c>
-      <c r="B149" s="9" t="s">
-        <v>275</v>
+      <c r="B149" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="C149" s="5">
         <v>6</v>
       </c>
-      <c r="D149" s="12" t="s">
+      <c r="D149" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4303,41 +4293,41 @@
       <c r="A150" s="5">
         <v>149</v>
       </c>
-      <c r="B150" s="9" t="s">
-        <v>276</v>
+      <c r="B150" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="C150" s="5">
         <v>6</v>
       </c>
-      <c r="D150" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D150" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>150</v>
       </c>
-      <c r="B151" s="9" t="s">
-        <v>277</v>
+      <c r="B151" s="8" t="s">
+        <v>275</v>
       </c>
       <c r="C151" s="5">
         <v>6</v>
       </c>
-      <c r="D151" s="12" t="s">
+      <c r="D151" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>151</v>
       </c>
-      <c r="B152" s="9" t="s">
-        <v>278</v>
+      <c r="B152" s="8" t="s">
+        <v>276</v>
       </c>
       <c r="C152" s="5">
         <v>6</v>
       </c>
-      <c r="D152" s="12" t="s">
+      <c r="D152" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4345,79 +4335,79 @@
       <c r="A153" s="5">
         <v>152</v>
       </c>
-      <c r="B153" s="9" t="s">
-        <v>279</v>
+      <c r="B153" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="C153" s="5">
         <v>6</v>
       </c>
-      <c r="D153" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D153" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>153</v>
       </c>
-      <c r="B154" s="9" t="s">
-        <v>280</v>
+      <c r="B154" s="8" t="s">
+        <v>278</v>
       </c>
       <c r="C154" s="5">
         <v>6</v>
       </c>
-      <c r="D154" s="12" t="s">
+      <c r="D154" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>154</v>
       </c>
-      <c r="B155" s="9" t="s">
-        <v>281</v>
+      <c r="B155" s="8" t="s">
+        <v>279</v>
       </c>
       <c r="C155" s="5">
         <v>6</v>
       </c>
-      <c r="D155" s="13"/>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D155" s="22"/>
+    </row>
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
         <v>155</v>
       </c>
-      <c r="B156" s="9" t="s">
-        <v>282</v>
+      <c r="B156" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="C156" s="5">
         <v>6</v>
       </c>
-      <c r="D156" s="13"/>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D156" s="22"/>
+    </row>
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>156</v>
       </c>
-      <c r="B157" s="9" t="s">
-        <v>283</v>
+      <c r="B157" s="8" t="s">
+        <v>281</v>
       </c>
       <c r="C157" s="5">
         <v>6</v>
       </c>
-      <c r="D157" s="12" t="s">
+      <c r="D157" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>157</v>
       </c>
-      <c r="B158" s="9" t="s">
-        <v>284</v>
+      <c r="B158" s="8" t="s">
+        <v>282</v>
       </c>
       <c r="C158" s="5">
         <v>6</v>
       </c>
-      <c r="D158" s="12" t="s">
+      <c r="D158" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4425,27 +4415,27 @@
       <c r="A159" s="5">
         <v>158</v>
       </c>
-      <c r="B159" s="9" t="s">
-        <v>285</v>
+      <c r="B159" s="8" t="s">
+        <v>283</v>
       </c>
       <c r="C159" s="5">
         <v>6</v>
       </c>
-      <c r="D159" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D159" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>159</v>
       </c>
-      <c r="B160" s="9" t="s">
-        <v>286</v>
+      <c r="B160" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="C160" s="5">
         <v>6</v>
       </c>
-      <c r="D160" s="12" t="s">
+      <c r="D160" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4453,27 +4443,27 @@
       <c r="A161" s="5">
         <v>160</v>
       </c>
-      <c r="B161" s="9" t="s">
-        <v>287</v>
+      <c r="B161" s="8" t="s">
+        <v>285</v>
       </c>
       <c r="C161" s="5">
         <v>6</v>
       </c>
-      <c r="D161" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D161" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>161</v>
       </c>
-      <c r="B162" s="9" t="s">
-        <v>288</v>
+      <c r="B162" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="C162" s="5">
         <v>6</v>
       </c>
-      <c r="D162" s="12" t="s">
+      <c r="D162" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4481,27 +4471,27 @@
       <c r="A163" s="5">
         <v>162</v>
       </c>
-      <c r="B163" s="9" t="s">
-        <v>289</v>
+      <c r="B163" s="8" t="s">
+        <v>287</v>
       </c>
       <c r="C163" s="5">
         <v>6</v>
       </c>
-      <c r="D163" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D163" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>163</v>
       </c>
-      <c r="B164" s="9" t="s">
-        <v>290</v>
+      <c r="B164" s="8" t="s">
+        <v>288</v>
       </c>
       <c r="C164" s="5">
         <v>6</v>
       </c>
-      <c r="D164" s="12" t="s">
+      <c r="D164" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4509,95 +4499,95 @@
       <c r="A165" s="5">
         <v>164</v>
       </c>
-      <c r="B165" s="9" t="s">
-        <v>291</v>
+      <c r="B165" s="8" t="s">
+        <v>289</v>
       </c>
       <c r="C165" s="5">
         <v>6</v>
       </c>
-      <c r="D165" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D165" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>165</v>
       </c>
-      <c r="B166" s="9" t="s">
+      <c r="B166" s="8" t="s">
         <v>86</v>
       </c>
       <c r="C166" s="5">
         <v>6</v>
       </c>
-      <c r="D166" s="12" t="s">
+      <c r="D166" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>166</v>
       </c>
-      <c r="B167" s="9" t="s">
-        <v>292</v>
+      <c r="B167" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="C167" s="5">
         <v>6</v>
       </c>
-      <c r="D167" s="12" t="s">
+      <c r="D167" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>167</v>
       </c>
-      <c r="B168" s="9" t="s">
-        <v>293</v>
+      <c r="B168" s="8" t="s">
+        <v>291</v>
       </c>
       <c r="C168" s="5">
         <v>6</v>
       </c>
-      <c r="D168" s="12" t="s">
+      <c r="D168" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>168</v>
       </c>
-      <c r="B169" s="9" t="s">
-        <v>294</v>
+      <c r="B169" s="8" t="s">
+        <v>292</v>
       </c>
       <c r="C169" s="5">
         <v>6</v>
       </c>
-      <c r="D169" s="12" t="s">
+      <c r="D169" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>169</v>
       </c>
-      <c r="B170" s="9" t="s">
-        <v>295</v>
+      <c r="B170" s="8" t="s">
+        <v>293</v>
       </c>
       <c r="C170" s="5">
         <v>6</v>
       </c>
-      <c r="D170" s="13"/>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D170" s="22"/>
+    </row>
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>170</v>
       </c>
-      <c r="B171" s="9" t="s">
+      <c r="B171" s="8" t="s">
         <v>87</v>
       </c>
       <c r="C171" s="5">
         <v>6</v>
       </c>
-      <c r="D171" s="12" t="s">
+      <c r="D171" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4605,121 +4595,121 @@
       <c r="A172" s="5">
         <v>171</v>
       </c>
-      <c r="B172" s="9" t="s">
-        <v>296</v>
+      <c r="B172" s="8" t="s">
+        <v>294</v>
       </c>
       <c r="C172" s="5">
         <v>6</v>
       </c>
-      <c r="D172" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D172" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>172</v>
       </c>
-      <c r="B173" s="9" t="s">
-        <v>297</v>
+      <c r="B173" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="C173" s="5">
         <v>6</v>
       </c>
-      <c r="D173" s="12" t="s">
+      <c r="D173" s="20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>173</v>
       </c>
-      <c r="B174" s="9" t="s">
-        <v>298</v>
+      <c r="B174" s="8" t="s">
+        <v>296</v>
       </c>
       <c r="C174" s="5">
         <v>6</v>
       </c>
-      <c r="D174" s="13"/>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D174" s="22"/>
+    </row>
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>174</v>
       </c>
-      <c r="B175" s="9" t="s">
-        <v>299</v>
+      <c r="B175" s="8" t="s">
+        <v>297</v>
       </c>
       <c r="C175" s="5">
         <v>6</v>
       </c>
-      <c r="D175" s="12" t="s">
+      <c r="D175" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>175</v>
       </c>
-      <c r="B176" s="9" t="s">
-        <v>300</v>
+      <c r="B176" s="8" t="s">
+        <v>298</v>
       </c>
       <c r="C176" s="5">
         <v>6</v>
       </c>
-      <c r="D176" s="12" t="s">
+      <c r="D176" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>176</v>
       </c>
-      <c r="B177" s="9" t="s">
-        <v>301</v>
+      <c r="B177" s="8" t="s">
+        <v>299</v>
       </c>
       <c r="C177" s="5">
         <v>6</v>
       </c>
-      <c r="D177" s="12" t="s">
+      <c r="D177" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>177</v>
       </c>
-      <c r="B178" s="9" t="s">
-        <v>302</v>
+      <c r="B178" s="8" t="s">
+        <v>300</v>
       </c>
       <c r="C178" s="5">
         <v>6</v>
       </c>
-      <c r="D178" s="12" t="s">
+      <c r="D178" s="20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>178</v>
       </c>
-      <c r="B179" s="9" t="s">
-        <v>303</v>
+      <c r="B179" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="C179" s="5">
         <v>6</v>
       </c>
-      <c r="D179" s="13"/>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D179" s="22"/>
+    </row>
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>179</v>
       </c>
-      <c r="B180" s="9" t="s">
-        <v>304</v>
+      <c r="B180" s="8" t="s">
+        <v>302</v>
       </c>
       <c r="C180" s="5">
         <v>6</v>
       </c>
-      <c r="D180" s="12" t="s">
+      <c r="D180" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4727,109 +4717,109 @@
       <c r="A181" s="5">
         <v>180</v>
       </c>
-      <c r="B181" s="9" t="s">
-        <v>305</v>
+      <c r="B181" s="8" t="s">
+        <v>303</v>
       </c>
       <c r="C181" s="5">
         <v>6</v>
       </c>
-      <c r="D181" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D181" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>181</v>
       </c>
-      <c r="B182" s="9" t="s">
-        <v>306</v>
+      <c r="B182" s="8" t="s">
+        <v>304</v>
       </c>
       <c r="C182" s="5">
         <v>6</v>
       </c>
-      <c r="D182" s="13"/>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D182" s="22"/>
+    </row>
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>182</v>
       </c>
-      <c r="B183" s="9" t="s">
-        <v>307</v>
+      <c r="B183" s="8" t="s">
+        <v>305</v>
       </c>
       <c r="C183" s="5">
         <v>6</v>
       </c>
-      <c r="D183" s="12" t="s">
+      <c r="D183" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>183</v>
       </c>
-      <c r="B184" s="9" t="s">
-        <v>308</v>
+      <c r="B184" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C184" s="5">
         <v>6</v>
       </c>
-      <c r="D184" s="12" t="s">
+      <c r="D184" s="20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>184</v>
       </c>
-      <c r="B185" s="9" t="s">
-        <v>309</v>
+      <c r="B185" s="8" t="s">
+        <v>307</v>
       </c>
       <c r="C185" s="5">
         <v>6</v>
       </c>
-      <c r="D185" s="12" t="s">
+      <c r="D185" s="20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>185</v>
       </c>
-      <c r="B186" s="9" t="s">
-        <v>310</v>
+      <c r="B186" s="8" t="s">
+        <v>308</v>
       </c>
       <c r="C186" s="5">
         <v>6</v>
       </c>
-      <c r="D186" s="12" t="s">
+      <c r="D186" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>186</v>
       </c>
-      <c r="B187" s="9" t="s">
-        <v>311</v>
+      <c r="B187" s="8" t="s">
+        <v>309</v>
       </c>
       <c r="C187" s="5">
         <v>6</v>
       </c>
-      <c r="D187" s="12" t="s">
+      <c r="D187" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>187</v>
       </c>
-      <c r="B188" s="9" t="s">
-        <v>312</v>
+      <c r="B188" s="8" t="s">
+        <v>310</v>
       </c>
       <c r="C188" s="5">
         <v>6</v>
       </c>
-      <c r="D188" s="12" t="s">
+      <c r="D188" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4838,12 +4828,12 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C189" s="5">
         <v>6</v>
       </c>
-      <c r="D189" s="12" t="s">
+      <c r="D189" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4851,13 +4841,13 @@
       <c r="A190" s="5">
         <v>189</v>
       </c>
-      <c r="B190" s="9" t="s">
-        <v>314</v>
+      <c r="B190" s="8" t="s">
+        <v>312</v>
       </c>
       <c r="C190" s="5">
         <v>7</v>
       </c>
-      <c r="D190" s="9" t="s">
+      <c r="D190" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4865,13 +4855,13 @@
       <c r="A191" s="5">
         <v>190</v>
       </c>
-      <c r="B191" s="9" t="s">
-        <v>315</v>
+      <c r="B191" s="8" t="s">
+        <v>313</v>
       </c>
       <c r="C191" s="5">
         <v>7</v>
       </c>
-      <c r="D191" s="9" t="s">
+      <c r="D191" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4879,13 +4869,13 @@
       <c r="A192" s="5">
         <v>191</v>
       </c>
-      <c r="B192" s="9" t="s">
-        <v>316</v>
+      <c r="B192" s="8" t="s">
+        <v>314</v>
       </c>
       <c r="C192" s="5">
         <v>7</v>
       </c>
-      <c r="D192" s="9" t="s">
+      <c r="D192" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4893,27 +4883,27 @@
       <c r="A193" s="5">
         <v>192</v>
       </c>
-      <c r="B193" s="9" t="s">
-        <v>317</v>
+      <c r="B193" s="8" t="s">
+        <v>315</v>
       </c>
       <c r="C193" s="5">
         <v>7</v>
       </c>
-      <c r="D193" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D193" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
         <v>193</v>
       </c>
-      <c r="B194" s="9" t="s">
-        <v>318</v>
+      <c r="B194" s="8" t="s">
+        <v>316</v>
       </c>
       <c r="C194" s="5">
         <v>7</v>
       </c>
-      <c r="D194" s="9" t="s">
+      <c r="D194" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4921,13 +4911,13 @@
       <c r="A195" s="5">
         <v>194</v>
       </c>
-      <c r="B195" s="9" t="s">
-        <v>319</v>
+      <c r="B195" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="C195" s="5">
         <v>7</v>
       </c>
-      <c r="D195" s="9" t="s">
+      <c r="D195" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4935,69 +4925,69 @@
       <c r="A196" s="5">
         <v>195</v>
       </c>
-      <c r="B196" s="9" t="s">
-        <v>320</v>
+      <c r="B196" s="8" t="s">
+        <v>318</v>
       </c>
       <c r="C196" s="5">
         <v>7</v>
       </c>
-      <c r="D196" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D196" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>196</v>
       </c>
-      <c r="B197" s="9" t="s">
-        <v>321</v>
+      <c r="B197" s="8" t="s">
+        <v>319</v>
       </c>
       <c r="C197" s="5">
         <v>7</v>
       </c>
-      <c r="D197" s="9" t="s">
+      <c r="D197" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>197</v>
       </c>
-      <c r="B198" s="9" t="s">
-        <v>322</v>
+      <c r="B198" s="8" t="s">
+        <v>320</v>
       </c>
       <c r="C198" s="5">
         <v>7</v>
       </c>
-      <c r="D198" s="9" t="s">
+      <c r="D198" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>198</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C199" s="5">
         <v>8</v>
       </c>
-      <c r="D199" s="9" t="s">
+      <c r="D199" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
         <v>199</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C200" s="5">
         <v>8</v>
       </c>
-      <c r="D200" s="9" t="s">
+      <c r="D200" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -5006,12 +4996,12 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C201" s="5">
         <v>8</v>
       </c>
-      <c r="D201" s="9" t="s">
+      <c r="D201" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5020,12 +5010,12 @@
         <v>201</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C202" s="5">
         <v>8</v>
       </c>
-      <c r="D202" s="9" t="s">
+      <c r="D202" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5034,12 +5024,12 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C203" s="5">
         <v>8</v>
       </c>
-      <c r="D203" s="9" t="s">
+      <c r="D203" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5048,26 +5038,26 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C204" s="5">
         <v>8</v>
       </c>
-      <c r="D204" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D204" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C205" s="5">
         <v>8</v>
       </c>
-      <c r="D205" s="9" t="s">
+      <c r="D205" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5076,12 +5066,12 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C206" s="5">
         <v>8</v>
       </c>
-      <c r="D206" s="9" t="s">
+      <c r="D206" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5090,12 +5080,12 @@
         <v>206</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C207" s="5">
         <v>8</v>
       </c>
-      <c r="D207" s="9" t="s">
+      <c r="D207" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5104,12 +5094,12 @@
         <v>207</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C208" s="5">
         <v>8</v>
       </c>
-      <c r="D208" s="9" t="s">
+      <c r="D208" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5118,12 +5108,12 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C209" s="5">
         <v>8</v>
       </c>
-      <c r="D209" s="9" t="s">
+      <c r="D209" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5132,40 +5122,40 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C210" s="5">
         <v>8</v>
       </c>
-      <c r="D210" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D210" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>210</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C211" s="5">
         <v>8</v>
       </c>
-      <c r="D211" s="9" t="s">
+      <c r="D211" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>211</v>
       </c>
-      <c r="B212" s="14" t="s">
-        <v>98</v>
+      <c r="B212" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="C212" s="5">
         <v>8</v>
       </c>
-      <c r="D212" s="9" t="s">
+      <c r="D212" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5173,13 +5163,13 @@
       <c r="A213" s="5">
         <v>212</v>
       </c>
-      <c r="B213" s="14" t="s">
-        <v>99</v>
+      <c r="B213" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="C213" s="5">
         <v>8</v>
       </c>
-      <c r="D213" s="9" t="s">
+      <c r="D213" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5187,13 +5177,13 @@
       <c r="A214" s="5">
         <v>213</v>
       </c>
-      <c r="B214" s="14" t="s">
-        <v>100</v>
+      <c r="B214" s="10" t="s">
+        <v>99</v>
       </c>
       <c r="C214" s="5">
         <v>8</v>
       </c>
-      <c r="D214" s="9" t="s">
+      <c r="D214" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5201,13 +5191,13 @@
       <c r="A215" s="5">
         <v>214</v>
       </c>
-      <c r="B215" s="14" t="s">
-        <v>101</v>
+      <c r="B215" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="C215" s="5">
         <v>8</v>
       </c>
-      <c r="D215" s="9" t="s">
+      <c r="D215" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5215,13 +5205,13 @@
       <c r="A216" s="5">
         <v>215</v>
       </c>
-      <c r="B216" s="14" t="s">
-        <v>102</v>
+      <c r="B216" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="C216" s="5">
         <v>8</v>
       </c>
-      <c r="D216" s="9" t="s">
+      <c r="D216" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5229,13 +5219,13 @@
       <c r="A217" s="5">
         <v>216</v>
       </c>
-      <c r="B217" s="14" t="s">
-        <v>103</v>
+      <c r="B217" s="10" t="s">
+        <v>102</v>
       </c>
       <c r="C217" s="5">
         <v>8</v>
       </c>
-      <c r="D217" s="9" t="s">
+      <c r="D217" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5243,27 +5233,27 @@
       <c r="A218" s="5">
         <v>217</v>
       </c>
-      <c r="B218" s="14" t="s">
-        <v>104</v>
+      <c r="B218" s="10" t="s">
+        <v>103</v>
       </c>
       <c r="C218" s="5">
         <v>8</v>
       </c>
-      <c r="D218" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D218" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>218</v>
       </c>
-      <c r="B219" s="15" t="s">
-        <v>105</v>
+      <c r="B219" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="C219" s="5">
         <v>8</v>
       </c>
-      <c r="D219" s="9" t="s">
+      <c r="D219" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5272,12 +5262,12 @@
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C220" s="5">
         <v>9</v>
       </c>
-      <c r="D220" s="9" t="s">
+      <c r="D220" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5286,12 +5276,12 @@
         <v>220</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C221" s="5">
         <v>9</v>
       </c>
-      <c r="D221" s="9" t="s">
+      <c r="D221" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5300,12 +5290,12 @@
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C222" s="5">
         <v>9</v>
       </c>
-      <c r="D222" s="9" t="s">
+      <c r="D222" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5313,13 +5303,13 @@
       <c r="A223" s="5">
         <v>222</v>
       </c>
-      <c r="B223" s="9" t="s">
-        <v>331</v>
+      <c r="B223" s="8" t="s">
+        <v>329</v>
       </c>
       <c r="C223" s="5">
         <v>9</v>
       </c>
-      <c r="D223" s="9" t="s">
+      <c r="D223" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5328,12 +5318,12 @@
         <v>223</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C224" s="5">
         <v>9</v>
       </c>
-      <c r="D224" s="9" t="s">
+      <c r="D224" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5341,13 +5331,13 @@
       <c r="A225" s="5">
         <v>224</v>
       </c>
-      <c r="B225" s="9" t="s">
-        <v>107</v>
+      <c r="B225" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="C225" s="5">
         <v>9</v>
       </c>
-      <c r="D225" s="9" t="s">
+      <c r="D225" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5355,13 +5345,13 @@
       <c r="A226" s="5">
         <v>225</v>
       </c>
-      <c r="B226" s="8" t="s">
-        <v>108</v>
+      <c r="B226" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="C226" s="5">
         <v>9</v>
       </c>
-      <c r="D226" s="9" t="s">
+      <c r="D226" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5369,13 +5359,13 @@
       <c r="A227" s="5">
         <v>226</v>
       </c>
-      <c r="B227" s="8" t="s">
-        <v>109</v>
+      <c r="B227" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="C227" s="5">
         <v>9</v>
       </c>
-      <c r="D227" s="9" t="s">
+      <c r="D227" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5383,13 +5373,13 @@
       <c r="A228" s="5">
         <v>227</v>
       </c>
-      <c r="B228" s="9" t="s">
-        <v>333</v>
+      <c r="B228" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="C228" s="5">
         <v>10</v>
       </c>
-      <c r="D228" s="9" t="s">
+      <c r="D228" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5397,13 +5387,13 @@
       <c r="A229" s="5">
         <v>228</v>
       </c>
-      <c r="B229" s="9" t="s">
-        <v>334</v>
+      <c r="B229" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="C229" s="5">
         <v>10</v>
       </c>
-      <c r="D229" s="9" t="s">
+      <c r="D229" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5411,13 +5401,13 @@
       <c r="A230" s="5">
         <v>229</v>
       </c>
-      <c r="B230" s="9" t="s">
-        <v>110</v>
+      <c r="B230" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="C230" s="5">
         <v>10</v>
       </c>
-      <c r="D230" s="9" t="s">
+      <c r="D230" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5425,13 +5415,13 @@
       <c r="A231" s="5">
         <v>230</v>
       </c>
-      <c r="B231" s="9" t="s">
-        <v>111</v>
+      <c r="B231" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="C231" s="5">
         <v>10</v>
       </c>
-      <c r="D231" s="9" t="s">
+      <c r="D231" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5439,13 +5429,13 @@
       <c r="A232" s="5">
         <v>231</v>
       </c>
-      <c r="B232" s="9" t="s">
-        <v>335</v>
+      <c r="B232" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="C232" s="5">
         <v>10</v>
       </c>
-      <c r="D232" s="9" t="s">
+      <c r="D232" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5453,27 +5443,27 @@
       <c r="A233" s="5">
         <v>232</v>
       </c>
-      <c r="B233" s="9" t="s">
-        <v>112</v>
+      <c r="B233" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="C233" s="5">
         <v>10</v>
       </c>
-      <c r="D233" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D233" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
         <v>233</v>
       </c>
-      <c r="B234" s="9" t="s">
-        <v>336</v>
+      <c r="B234" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C234" s="5">
         <v>10</v>
       </c>
-      <c r="D234" s="9" t="s">
+      <c r="D234" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5481,13 +5471,13 @@
       <c r="A235" s="5">
         <v>234</v>
       </c>
-      <c r="B235" s="9" t="s">
-        <v>113</v>
+      <c r="B235" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="C235" s="5">
         <v>10</v>
       </c>
-      <c r="D235" s="9" t="s">
+      <c r="D235" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5495,27 +5485,27 @@
       <c r="A236" s="5">
         <v>235</v>
       </c>
-      <c r="B236" s="9" t="s">
-        <v>337</v>
+      <c r="B236" s="8" t="s">
+        <v>335</v>
       </c>
       <c r="C236" s="5">
         <v>10</v>
       </c>
-      <c r="D236" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D236" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>236</v>
       </c>
-      <c r="B237" s="9" t="s">
-        <v>338</v>
+      <c r="B237" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C237" s="5">
         <v>10</v>
       </c>
-      <c r="D237" s="9" t="s">
+      <c r="D237" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5523,13 +5513,13 @@
       <c r="A238" s="5">
         <v>237</v>
       </c>
-      <c r="B238" s="9" t="s">
-        <v>114</v>
+      <c r="B238" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="C238" s="5">
         <v>10</v>
       </c>
-      <c r="D238" s="9" t="s">
+      <c r="D238" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5537,13 +5527,13 @@
       <c r="A239" s="5">
         <v>238</v>
       </c>
-      <c r="B239" s="9" t="s">
-        <v>339</v>
+      <c r="B239" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C239" s="5">
         <v>10</v>
       </c>
-      <c r="D239" s="9" t="s">
+      <c r="D239" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5551,13 +5541,13 @@
       <c r="A240" s="5">
         <v>239</v>
       </c>
-      <c r="B240" s="9" t="s">
-        <v>340</v>
+      <c r="B240" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="C240" s="5">
         <v>10</v>
       </c>
-      <c r="D240" s="9" t="s">
+      <c r="D240" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5565,53 +5555,53 @@
       <c r="A241" s="5">
         <v>240</v>
       </c>
-      <c r="B241" s="9" t="s">
-        <v>115</v>
+      <c r="B241" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="C241" s="5">
         <v>10</v>
       </c>
-      <c r="D241" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D241" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
         <v>241</v>
       </c>
-      <c r="B242" s="9" t="s">
-        <v>341</v>
+      <c r="B242" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C242" s="5">
         <v>10</v>
       </c>
-      <c r="D242" s="10"/>
+      <c r="D242" s="21"/>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>242</v>
       </c>
-      <c r="B243" s="9" t="s">
-        <v>342</v>
+      <c r="B243" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C243" s="5">
         <v>10</v>
       </c>
-      <c r="D243" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D243" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="5">
         <v>243</v>
       </c>
-      <c r="B244" s="9" t="s">
-        <v>343</v>
+      <c r="B244" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="C244" s="5">
         <v>10</v>
       </c>
-      <c r="D244" s="9" t="s">
+      <c r="D244" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5619,39 +5609,39 @@
       <c r="A245" s="5">
         <v>244</v>
       </c>
-      <c r="B245" s="9" t="s">
-        <v>344</v>
+      <c r="B245" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C245" s="5">
         <v>11</v>
       </c>
-      <c r="D245" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D245" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
         <v>245</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C246" s="5">
         <v>11</v>
       </c>
-      <c r="D246" s="10"/>
+      <c r="D246" s="21"/>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
         <v>246</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C247" s="5">
         <v>11</v>
       </c>
-      <c r="D247" s="9" t="s">
+      <c r="D247" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5660,27 +5650,27 @@
         <v>247</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C248" s="5">
         <v>11</v>
       </c>
-      <c r="D248" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D248" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
         <v>248</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C249" s="5">
         <v>11</v>
       </c>
-      <c r="D249" s="9" t="s">
-        <v>120</v>
+      <c r="D249" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
@@ -5688,12 +5678,12 @@
         <v>249</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C250" s="5">
         <v>11</v>
       </c>
-      <c r="D250" s="9" t="s">
+      <c r="D250" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5702,26 +5692,26 @@
         <v>250</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C251" s="5">
         <v>11</v>
       </c>
-      <c r="D251" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D251" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
         <v>251</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C252" s="5">
         <v>11</v>
       </c>
-      <c r="D252" s="9" t="s">
+      <c r="D252" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -5730,12 +5720,12 @@
         <v>252</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C253" s="5">
         <v>11</v>
       </c>
-      <c r="D253" s="9" t="s">
+      <c r="D253" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5744,12 +5734,12 @@
         <v>253</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C254" s="5">
         <v>11</v>
       </c>
-      <c r="D254" s="9" t="s">
+      <c r="D254" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5758,12 +5748,12 @@
         <v>254</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C255" s="5">
         <v>11</v>
       </c>
-      <c r="D255" s="9" t="s">
+      <c r="D255" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5772,12 +5762,12 @@
         <v>255</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C256" s="5">
         <v>11</v>
       </c>
-      <c r="D256" s="9" t="s">
+      <c r="D256" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5786,12 +5776,12 @@
         <v>256</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C257" s="5">
         <v>11</v>
       </c>
-      <c r="D257" s="9" t="s">
+      <c r="D257" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5800,12 +5790,12 @@
         <v>257</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C258" s="5">
         <v>11</v>
       </c>
-      <c r="D258" s="9" t="s">
+      <c r="D258" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5814,12 +5804,12 @@
         <v>258</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C259" s="5">
         <v>11</v>
       </c>
-      <c r="D259" s="9" t="s">
+      <c r="D259" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5828,12 +5818,12 @@
         <v>259</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C260" s="5">
         <v>11</v>
       </c>
-      <c r="D260" s="9" t="s">
+      <c r="D260" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5842,12 +5832,12 @@
         <v>260</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C261" s="5">
         <v>11</v>
       </c>
-      <c r="D261" s="9" t="s">
+      <c r="D261" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5856,26 +5846,26 @@
         <v>261</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C262" s="5">
         <v>11</v>
       </c>
-      <c r="D262" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D262" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="5">
         <v>262</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C263" s="5">
         <v>11</v>
       </c>
-      <c r="D263" s="9" t="s">
+      <c r="D263" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5884,13 +5874,13 @@
         <v>263</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C264" s="5">
         <v>11</v>
       </c>
-      <c r="D264" s="9" t="s">
-        <v>90</v>
+      <c r="D264" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
@@ -5898,13 +5888,13 @@
         <v>264</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C265" s="5">
         <v>11</v>
       </c>
-      <c r="D265" s="9" t="s">
-        <v>90</v>
+      <c r="D265" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
@@ -5912,26 +5902,26 @@
         <v>265</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C266" s="5">
         <v>12</v>
       </c>
-      <c r="D266" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D266" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
         <v>266</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C267" s="5">
         <v>12</v>
       </c>
-      <c r="D267" s="16" t="s">
+      <c r="D267" s="23" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5940,12 +5930,12 @@
         <v>267</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C268" s="5">
         <v>12</v>
       </c>
-      <c r="D268" s="16" t="s">
+      <c r="D268" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5954,12 +5944,12 @@
         <v>268</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C269" s="5">
         <v>12</v>
       </c>
-      <c r="D269" s="16" t="s">
+      <c r="D269" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5968,12 +5958,12 @@
         <v>269</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C270" s="5">
         <v>12</v>
       </c>
-      <c r="D270" s="16" t="s">
+      <c r="D270" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5982,26 +5972,26 @@
         <v>270</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C271" s="5">
         <v>12</v>
       </c>
-      <c r="D271" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D271" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="5">
         <v>271</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C272" s="5">
         <v>12</v>
       </c>
-      <c r="D272" s="16" t="s">
+      <c r="D272" s="23" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6010,12 +6000,12 @@
         <v>272</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C273" s="5">
         <v>12</v>
       </c>
-      <c r="D273" s="16" t="s">
+      <c r="D273" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6024,12 +6014,12 @@
         <v>273</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C274" s="5">
         <v>12</v>
       </c>
-      <c r="D274" s="16" t="s">
+      <c r="D274" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6038,12 +6028,12 @@
         <v>274</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C275" s="5">
         <v>12</v>
       </c>
-      <c r="D275" s="16" t="s">
+      <c r="D275" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6052,12 +6042,12 @@
         <v>275</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C276" s="5">
         <v>12</v>
       </c>
-      <c r="D276" s="16" t="s">
+      <c r="D276" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6066,12 +6056,12 @@
         <v>276</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C277" s="5">
         <v>12</v>
       </c>
-      <c r="D277" s="16" t="s">
+      <c r="D277" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6080,12 +6070,12 @@
         <v>277</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C278" s="5">
         <v>12</v>
       </c>
-      <c r="D278" s="16" t="s">
+      <c r="D278" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6094,26 +6084,26 @@
         <v>278</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C279" s="5">
         <v>12</v>
       </c>
-      <c r="D279" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D279" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="5">
         <v>279</v>
       </c>
-      <c r="B280" s="17" t="s">
-        <v>127</v>
+      <c r="B280" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C280" s="5">
         <v>12</v>
       </c>
-      <c r="D280" s="16" t="s">
+      <c r="D280" s="23" t="s">
         <v>88</v>
       </c>
     </row>
@@ -6121,13 +6111,13 @@
       <c r="A281" s="5">
         <v>280</v>
       </c>
-      <c r="B281" s="9" t="s">
-        <v>175</v>
+      <c r="B281" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C281" s="5">
         <v>13</v>
       </c>
-      <c r="D281" s="16" t="s">
+      <c r="D281" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6135,13 +6125,13 @@
       <c r="A282" s="5">
         <v>281</v>
       </c>
-      <c r="B282" s="9" t="s">
-        <v>128</v>
+      <c r="B282" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="C282" s="5">
         <v>13</v>
       </c>
-      <c r="D282" s="16" t="s">
+      <c r="D282" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6150,12 +6140,12 @@
         <v>282</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C283" s="5">
         <v>13</v>
       </c>
-      <c r="D283" s="16" t="s">
+      <c r="D283" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6164,40 +6154,40 @@
         <v>283</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C284" s="5">
         <v>13</v>
       </c>
-      <c r="D284" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D284" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="5">
         <v>284</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C285" s="5">
         <v>13</v>
       </c>
-      <c r="D285" s="16" t="s">
+      <c r="D285" s="23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
         <v>285</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C286" s="5">
         <v>13</v>
       </c>
-      <c r="D286" s="16" t="s">
+      <c r="D286" s="23" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6206,12 +6196,12 @@
         <v>286</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C287" s="5">
         <v>13</v>
       </c>
-      <c r="D287" s="16" t="s">
+      <c r="D287" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6220,12 +6210,12 @@
         <v>287</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C288" s="5">
         <v>13</v>
       </c>
-      <c r="D288" s="16" t="s">
+      <c r="D288" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6234,12 +6224,12 @@
         <v>288</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C289" s="5">
         <v>13</v>
       </c>
-      <c r="D289" s="16" t="s">
+      <c r="D289" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6248,12 +6238,12 @@
         <v>289</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C290" s="5">
         <v>13</v>
       </c>
-      <c r="D290" s="16" t="s">
+      <c r="D290" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6262,12 +6252,12 @@
         <v>290</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C291" s="5">
         <v>13</v>
       </c>
-      <c r="D291" s="16" t="s">
+      <c r="D291" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6276,26 +6266,26 @@
         <v>291</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C292" s="5">
         <v>13</v>
       </c>
-      <c r="D292" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D292" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="5">
         <v>292</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C293" s="5">
         <v>13</v>
       </c>
-      <c r="D293" s="16" t="s">
+      <c r="D293" s="23" t="s">
         <v>73</v>
       </c>
     </row>
@@ -6304,12 +6294,12 @@
         <v>293</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C294" s="5">
         <v>13</v>
       </c>
-      <c r="D294" s="16" t="s">
+      <c r="D294" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6318,12 +6308,12 @@
         <v>294</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C295" s="5">
         <v>13</v>
       </c>
-      <c r="D295" s="16" t="s">
+      <c r="D295" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6332,12 +6322,12 @@
         <v>295</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C296" s="5">
         <v>13</v>
       </c>
-      <c r="D296" s="16" t="s">
+      <c r="D296" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6346,26 +6336,26 @@
         <v>296</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C297" s="5">
         <v>13</v>
       </c>
-      <c r="D297" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D297" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="5">
         <v>297</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C298" s="5">
         <v>13</v>
       </c>
-      <c r="D298" s="16" t="s">
+      <c r="D298" s="23" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6374,12 +6364,12 @@
         <v>298</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C299" s="5">
         <v>13</v>
       </c>
-      <c r="D299" s="16" t="s">
+      <c r="D299" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6388,12 +6378,12 @@
         <v>299</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C300" s="5">
         <v>13</v>
       </c>
-      <c r="D300" s="16" t="s">
+      <c r="D300" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6402,12 +6392,12 @@
         <v>300</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C301" s="5">
         <v>13</v>
       </c>
-      <c r="D301" s="16" t="s">
+      <c r="D301" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6416,12 +6406,12 @@
         <v>301</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C302" s="5">
         <v>13</v>
       </c>
-      <c r="D302" s="16" t="s">
+      <c r="D302" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6430,12 +6420,12 @@
         <v>302</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C303" s="5">
         <v>13</v>
       </c>
-      <c r="D303" s="16" t="s">
+      <c r="D303" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6444,12 +6434,12 @@
         <v>303</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C304" s="5">
         <v>13</v>
       </c>
-      <c r="D304" s="16" t="s">
+      <c r="D304" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6458,12 +6448,12 @@
         <v>304</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C305" s="5">
         <v>13</v>
       </c>
-      <c r="D305" s="16" t="s">
+      <c r="D305" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6472,12 +6462,12 @@
         <v>305</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C306" s="5">
         <v>13</v>
       </c>
-      <c r="D306" s="16" t="s">
+      <c r="D306" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6486,12 +6476,12 @@
         <v>306</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C307" s="5">
         <v>13</v>
       </c>
-      <c r="D307" s="16" t="s">
+      <c r="D307" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6500,26 +6490,26 @@
         <v>307</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C308" s="5">
         <v>13</v>
       </c>
-      <c r="D308" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D308" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="5">
         <v>308</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C309" s="5">
         <v>13</v>
       </c>
-      <c r="D309" s="16" t="s">
+      <c r="D309" s="23" t="s">
         <v>73</v>
       </c>
     </row>
@@ -6528,12 +6518,12 @@
         <v>309</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C310" s="5">
         <v>13</v>
       </c>
-      <c r="D310" s="16" t="s">
+      <c r="D310" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6542,12 +6532,12 @@
         <v>310</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C311" s="5">
         <v>13</v>
       </c>
-      <c r="D311" s="16" t="s">
+      <c r="D311" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6556,12 +6546,12 @@
         <v>311</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C312" s="5">
         <v>13</v>
       </c>
-      <c r="D312" s="16" t="s">
+      <c r="D312" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6570,12 +6560,12 @@
         <v>312</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C313" s="5">
         <v>13</v>
       </c>
-      <c r="D313" s="16" t="s">
+      <c r="D313" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6584,12 +6574,12 @@
         <v>313</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C314" s="5">
         <v>13</v>
       </c>
-      <c r="D314" s="16" t="s">
+      <c r="D314" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6598,12 +6588,12 @@
         <v>314</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C315" s="5">
         <v>13</v>
       </c>
-      <c r="D315" s="16" t="s">
+      <c r="D315" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6612,26 +6602,26 @@
         <v>315</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C316" s="5">
         <v>13</v>
       </c>
-      <c r="D316" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D316" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="5">
         <v>316</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C317" s="5">
         <v>13</v>
       </c>
-      <c r="D317" s="16" t="s">
+      <c r="D317" s="23" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6640,54 +6630,54 @@
         <v>317</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C318" s="5">
         <v>13</v>
       </c>
-      <c r="D318" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D318" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="5">
         <v>318</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C319" s="5">
         <v>13</v>
       </c>
-      <c r="D319" s="16" t="s">
+      <c r="D319" s="23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="5">
         <v>319</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C320" s="5">
         <v>13</v>
       </c>
-      <c r="D320" s="16" t="s">
+      <c r="D320" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="5">
         <v>320</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C321" s="5">
         <v>13</v>
       </c>
-      <c r="D321" s="16" t="s">
+      <c r="D321" s="23" t="s">
         <v>75</v>
       </c>
     </row>
@@ -6696,12 +6686,12 @@
         <v>321</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C322" s="5">
         <v>13</v>
       </c>
-      <c r="D322" s="16" t="s">
+      <c r="D322" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6710,26 +6700,26 @@
         <v>322</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C323" s="5">
         <v>13</v>
       </c>
-      <c r="D323" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D323" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="5">
         <v>323</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C324" s="5">
         <v>13</v>
       </c>
-      <c r="D324" s="16" t="s">
+      <c r="D324" s="23" t="s">
         <v>73</v>
       </c>
     </row>
@@ -6738,12 +6728,12 @@
         <v>324</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C325" s="5">
         <v>13</v>
       </c>
-      <c r="D325" s="16" t="s">
+      <c r="D325" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6752,12 +6742,12 @@
         <v>325</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C326" s="5">
         <v>13</v>
       </c>
-      <c r="D326" s="16" t="s">
+      <c r="D326" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6766,12 +6756,12 @@
         <v>326</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C327" s="5">
         <v>13</v>
       </c>
-      <c r="D327" s="16" t="s">
+      <c r="D327" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6780,12 +6770,12 @@
         <v>327</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C328" s="5">
         <v>13</v>
       </c>
-      <c r="D328" s="16" t="s">
+      <c r="D328" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6794,12 +6784,12 @@
         <v>328</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C329" s="5">
         <v>13</v>
       </c>
-      <c r="D329" s="16" t="s">
+      <c r="D329" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6808,12 +6798,12 @@
         <v>329</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C330" s="5">
         <v>13</v>
       </c>
-      <c r="D330" s="16" t="s">
+      <c r="D330" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6822,12 +6812,12 @@
         <v>330</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C331" s="5">
         <v>13</v>
       </c>
-      <c r="D331" s="16" t="s">
+      <c r="D331" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6836,12 +6826,12 @@
         <v>331</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C332" s="5">
         <v>13</v>
       </c>
-      <c r="D332" s="16" t="s">
+      <c r="D332" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6850,26 +6840,26 @@
         <v>332</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C333" s="5">
         <v>13</v>
       </c>
-      <c r="D333" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D333" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="5">
         <v>333</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C334" s="5">
         <v>13</v>
       </c>
-      <c r="D334" s="16" t="s">
+      <c r="D334" s="23" t="s">
         <v>73</v>
       </c>
     </row>
@@ -6878,12 +6868,12 @@
         <v>334</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C335" s="5">
         <v>13</v>
       </c>
-      <c r="D335" s="16" t="s">
+      <c r="D335" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6892,12 +6882,12 @@
         <v>335</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C336" s="5">
         <v>13</v>
       </c>
-      <c r="D336" s="16" t="s">
+      <c r="D336" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6906,12 +6896,12 @@
         <v>336</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C337" s="5">
         <v>13</v>
       </c>
-      <c r="D337" s="16" t="s">
+      <c r="D337" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6920,12 +6910,12 @@
         <v>337</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C338" s="5">
         <v>13</v>
       </c>
-      <c r="D338" s="16" t="s">
+      <c r="D338" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6934,12 +6924,12 @@
         <v>338</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C339" s="5">
         <v>13</v>
       </c>
-      <c r="D339" s="16" t="s">
+      <c r="D339" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6948,12 +6938,12 @@
         <v>339</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C340" s="5">
         <v>13</v>
       </c>
-      <c r="D340" s="16" t="s">
+      <c r="D340" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6962,12 +6952,12 @@
         <v>340</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C341" s="5">
         <v>13</v>
       </c>
-      <c r="D341" s="16" t="s">
+      <c r="D341" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6976,12 +6966,12 @@
         <v>341</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C342" s="5">
         <v>13</v>
       </c>
-      <c r="D342" s="16" t="s">
+      <c r="D342" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6990,12 +6980,12 @@
         <v>342</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C343" s="5">
         <v>13</v>
       </c>
-      <c r="D343" s="16" t="s">
+      <c r="D343" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7004,12 +6994,12 @@
         <v>343</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C344" s="5">
         <v>13</v>
       </c>
-      <c r="D344" s="16" t="s">
+      <c r="D344" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7018,12 +7008,12 @@
         <v>344</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C345" s="5">
         <v>13</v>
       </c>
-      <c r="D345" s="16" t="s">
+      <c r="D345" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7032,26 +7022,26 @@
         <v>345</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C346" s="5">
         <v>14</v>
       </c>
-      <c r="D346" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D346" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="5">
         <v>346</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C347" s="5">
         <v>14</v>
       </c>
-      <c r="D347" s="7" t="s">
+      <c r="D347" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7060,26 +7050,26 @@
         <v>347</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C348" s="5">
         <v>14</v>
       </c>
-      <c r="D348" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D348" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="5">
         <v>348</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C349" s="5">
         <v>14</v>
       </c>
-      <c r="D349" s="7" t="s">
+      <c r="D349" s="20" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7088,12 +7078,12 @@
         <v>349</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C350" s="5">
         <v>15</v>
       </c>
-      <c r="D350" s="9" t="s">
+      <c r="D350" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7102,12 +7092,12 @@
         <v>350</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C351" s="5">
         <v>15</v>
       </c>
-      <c r="D351" s="9" t="s">
+      <c r="D351" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7116,12 +7106,12 @@
         <v>351</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C352" s="5">
         <v>15</v>
       </c>
-      <c r="D352" s="9" t="s">
+      <c r="D352" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7130,12 +7120,12 @@
         <v>352</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C353" s="5">
         <v>15</v>
       </c>
-      <c r="D353" s="9" t="s">
+      <c r="D353" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7144,12 +7134,12 @@
         <v>353</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C354" s="5">
         <v>15</v>
       </c>
-      <c r="D354" s="9" t="s">
+      <c r="D354" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7157,13 +7147,13 @@
       <c r="A355" s="5">
         <v>354</v>
       </c>
-      <c r="B355" s="9" t="s">
-        <v>137</v>
+      <c r="B355" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C355" s="5">
         <v>15</v>
       </c>
-      <c r="D355" s="9" t="s">
+      <c r="D355" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7172,38 +7162,38 @@
         <v>355</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C356" s="5">
         <v>15</v>
       </c>
-      <c r="D356" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D356" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="5">
         <v>356</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C357" s="5">
         <v>15</v>
       </c>
-      <c r="D357" s="10"/>
+      <c r="D357" s="21"/>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" s="5">
         <v>357</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C358" s="5">
         <v>15</v>
       </c>
-      <c r="D358" s="9" t="s">
+      <c r="D358" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7212,12 +7202,12 @@
         <v>358</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C359" s="5">
         <v>15</v>
       </c>
-      <c r="D359" s="9" t="s">
+      <c r="D359" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7226,104 +7216,104 @@
         <v>359</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C360" s="5">
         <v>15</v>
       </c>
-      <c r="D360" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D360" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="5">
         <v>360</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C361" s="5">
         <v>15</v>
       </c>
-      <c r="D361" s="10"/>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D361" s="21"/>
+    </row>
+    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="5">
         <v>361</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C362" s="5">
         <v>15</v>
       </c>
-      <c r="D362" s="9" t="s">
+      <c r="D362" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="5">
         <v>362</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C363" s="5">
         <v>15</v>
       </c>
-      <c r="D363" s="9" t="s">
+      <c r="D363" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="5">
         <v>363</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C364" s="5">
         <v>15</v>
       </c>
-      <c r="D364" s="10"/>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D364" s="21"/>
+    </row>
+    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="5">
         <v>364</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C365" s="5">
         <v>15</v>
       </c>
-      <c r="D365" s="9" t="s">
+      <c r="D365" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="5">
         <v>365</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C366" s="5">
         <v>15</v>
       </c>
-      <c r="D366" s="10"/>
+      <c r="D366" s="21"/>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="5">
         <v>366</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C367" s="5">
         <v>15</v>
       </c>
-      <c r="D367" s="9" t="s">
+      <c r="D367" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7332,12 +7322,12 @@
         <v>367</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C368" s="5">
         <v>15</v>
       </c>
-      <c r="D368" s="9" t="s">
+      <c r="D368" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7346,12 +7336,12 @@
         <v>368</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C369" s="5">
         <v>15</v>
       </c>
-      <c r="D369" s="9" t="s">
+      <c r="D369" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7360,12 +7350,12 @@
         <v>369</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C370" s="5">
         <v>15</v>
       </c>
-      <c r="D370" s="9" t="s">
+      <c r="D370" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7374,12 +7364,12 @@
         <v>370</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C371" s="5">
         <v>15</v>
       </c>
-      <c r="D371" s="9" t="s">
+      <c r="D371" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7388,12 +7378,12 @@
         <v>371</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C372" s="5">
         <v>15</v>
       </c>
-      <c r="D372" s="9" t="s">
+      <c r="D372" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7401,13 +7391,13 @@
       <c r="A373" s="5">
         <v>372</v>
       </c>
-      <c r="B373" s="18" t="s">
-        <v>146</v>
+      <c r="B373" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="C373" s="5">
         <v>15</v>
       </c>
-      <c r="D373" s="9" t="s">
+      <c r="D373" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7415,13 +7405,13 @@
       <c r="A374" s="5">
         <v>373</v>
       </c>
-      <c r="B374" s="18" t="s">
-        <v>147</v>
+      <c r="B374" s="13" t="s">
+        <v>145</v>
       </c>
       <c r="C374" s="5">
         <v>15</v>
       </c>
-      <c r="D374" s="9" t="s">
+      <c r="D374" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7429,13 +7419,13 @@
       <c r="A375" s="5">
         <v>374</v>
       </c>
-      <c r="B375" s="18" t="s">
-        <v>148</v>
+      <c r="B375" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="C375" s="5">
         <v>15</v>
       </c>
-      <c r="D375" s="9" t="s">
+      <c r="D375" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7444,12 +7434,12 @@
         <v>375</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C376" s="5">
         <v>16</v>
       </c>
-      <c r="D376" s="9" t="s">
+      <c r="D376" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7458,12 +7448,12 @@
         <v>376</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C377" s="5">
         <v>16</v>
       </c>
-      <c r="D377" s="9" t="s">
+      <c r="D377" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7472,12 +7462,12 @@
         <v>377</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C378" s="5">
         <v>16</v>
       </c>
-      <c r="D378" s="9" t="s">
+      <c r="D378" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7486,26 +7476,26 @@
         <v>378</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C379" s="5">
         <v>16</v>
       </c>
-      <c r="D379" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D379" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="5">
         <v>379</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C380" s="5">
         <v>16</v>
       </c>
-      <c r="D380" s="9" t="s">
+      <c r="D380" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7514,12 +7504,12 @@
         <v>380</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C381" s="5">
         <v>16</v>
       </c>
-      <c r="D381" s="9" t="s">
+      <c r="D381" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7528,26 +7518,26 @@
         <v>381</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C382" s="5">
         <v>16</v>
       </c>
-      <c r="D382" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D382" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="5">
         <v>382</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C383" s="5">
         <v>16</v>
       </c>
-      <c r="D383" s="9" t="s">
+      <c r="D383" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7556,12 +7546,12 @@
         <v>383</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C384" s="5">
         <v>16</v>
       </c>
-      <c r="D384" s="9" t="s">
+      <c r="D384" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7570,26 +7560,26 @@
         <v>384</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C385" s="5">
         <v>16</v>
       </c>
-      <c r="D385" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D385" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="5">
         <v>385</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C386" s="5">
         <v>16</v>
       </c>
-      <c r="D386" s="9" t="s">
+      <c r="D386" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7598,26 +7588,26 @@
         <v>386</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C387" s="5">
         <v>16</v>
       </c>
-      <c r="D387" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D387" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="5">
         <v>387</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C388" s="5">
         <v>16</v>
       </c>
-      <c r="D388" s="9" t="s">
+      <c r="D388" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7625,17 +7615,24 @@
       <c r="A389" s="5">
         <v>388</v>
       </c>
-      <c r="B389" s="19" t="s">
-        <v>153</v>
+      <c r="B389" s="14" t="s">
+        <v>151</v>
       </c>
       <c r="C389" s="5">
         <v>16</v>
       </c>
-      <c r="D389" s="6" t="s">
+      <c r="D389" s="24" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D389" xr:uid="{CD847B43-07E4-4458-A0B5-A7B3D7D8E6F7}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Teacher I"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -7902,931 +7899,931 @@
   <sheetFormatPr defaultColWidth="15.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>436</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="25" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="F1" s="26"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="25" t="s">
         <v>438</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="21" t="s">
+      <c r="I1" s="26"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="25" t="s">
         <v>439</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="21" t="s">
+      <c r="L1" s="26"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="25" t="s">
         <v>440</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="21" t="s">
+      <c r="O1" s="26"/>
+      <c r="P1" s="27"/>
+    </row>
+    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="29"/>
+      <c r="B2" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="L1" s="22"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="21" t="s">
+      <c r="C2" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="23"/>
-    </row>
-    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
-      <c r="B2" s="25" t="s">
+      <c r="D2" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="E2" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="B3" s="15">
+        <v>43</v>
+      </c>
+      <c r="C3" s="15">
+        <v>15</v>
+      </c>
+      <c r="D3" s="15">
+        <v>58</v>
+      </c>
+      <c r="E3" s="15">
+        <v>496</v>
+      </c>
+      <c r="F3" s="15">
+        <v>288</v>
+      </c>
+      <c r="G3" s="15">
+        <v>784</v>
+      </c>
+      <c r="H3" s="15">
+        <v>1399</v>
+      </c>
+      <c r="I3" s="15">
+        <v>1207</v>
+      </c>
+      <c r="J3" s="15">
+        <v>2606</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0</v>
+      </c>
+      <c r="L3" s="15">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15">
+        <v>0</v>
+      </c>
+      <c r="N3" s="15">
+        <v>1938</v>
+      </c>
+      <c r="O3" s="15">
+        <v>1510</v>
+      </c>
+      <c r="P3" s="15">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>445</v>
       </c>
-      <c r="E2" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="J2" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="K2" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="L2" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="M2" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="N2" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="O2" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="P2" s="25" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
+      <c r="B4" s="15">
+        <v>22</v>
+      </c>
+      <c r="C4" s="15">
+        <v>13</v>
+      </c>
+      <c r="D4" s="15">
+        <v>35</v>
+      </c>
+      <c r="E4" s="15">
+        <v>252</v>
+      </c>
+      <c r="F4" s="15">
+        <v>110</v>
+      </c>
+      <c r="G4" s="15">
+        <v>362</v>
+      </c>
+      <c r="H4" s="15">
+        <v>706</v>
+      </c>
+      <c r="I4" s="15">
+        <v>390</v>
+      </c>
+      <c r="J4" s="15">
+        <v>1096</v>
+      </c>
+      <c r="K4" s="15">
+        <v>0</v>
+      </c>
+      <c r="L4" s="15">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0</v>
+      </c>
+      <c r="N4" s="15">
+        <v>980</v>
+      </c>
+      <c r="O4" s="15">
+        <v>513</v>
+      </c>
+      <c r="P4" s="15">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="B3" s="25">
-        <v>43</v>
-      </c>
-      <c r="C3" s="25">
+      <c r="B5" s="15">
+        <v>27</v>
+      </c>
+      <c r="C5" s="15">
+        <v>9</v>
+      </c>
+      <c r="D5" s="15">
+        <v>36</v>
+      </c>
+      <c r="E5" s="15">
+        <v>116</v>
+      </c>
+      <c r="F5" s="15">
+        <v>182</v>
+      </c>
+      <c r="G5" s="15">
+        <v>298</v>
+      </c>
+      <c r="H5" s="15">
+        <v>249</v>
+      </c>
+      <c r="I5" s="15">
+        <v>175</v>
+      </c>
+      <c r="J5" s="15">
+        <v>424</v>
+      </c>
+      <c r="K5" s="15">
+        <v>0</v>
+      </c>
+      <c r="L5" s="15">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15">
+        <v>0</v>
+      </c>
+      <c r="N5" s="15">
+        <v>392</v>
+      </c>
+      <c r="O5" s="15">
+        <v>366</v>
+      </c>
+      <c r="P5" s="15">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B6" s="15">
+        <v>20</v>
+      </c>
+      <c r="C6" s="15">
+        <v>9</v>
+      </c>
+      <c r="D6" s="15">
+        <v>29</v>
+      </c>
+      <c r="E6" s="15">
+        <v>97</v>
+      </c>
+      <c r="F6" s="15">
+        <v>62</v>
+      </c>
+      <c r="G6" s="15">
+        <v>159</v>
+      </c>
+      <c r="H6" s="15">
+        <v>185</v>
+      </c>
+      <c r="I6" s="15">
+        <v>168</v>
+      </c>
+      <c r="J6" s="15">
+        <v>353</v>
+      </c>
+      <c r="K6" s="15">
+        <v>0</v>
+      </c>
+      <c r="L6" s="15">
+        <v>0</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0</v>
+      </c>
+      <c r="N6" s="15">
+        <v>302</v>
+      </c>
+      <c r="O6" s="15">
+        <v>239</v>
+      </c>
+      <c r="P6" s="15">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="B7" s="15">
+        <v>20</v>
+      </c>
+      <c r="C7" s="15">
+        <v>45</v>
+      </c>
+      <c r="D7" s="15">
+        <v>65</v>
+      </c>
+      <c r="E7" s="15">
+        <v>139</v>
+      </c>
+      <c r="F7" s="15">
+        <v>83</v>
+      </c>
+      <c r="G7" s="15">
+        <v>222</v>
+      </c>
+      <c r="H7" s="15">
+        <v>525</v>
+      </c>
+      <c r="I7" s="15">
+        <v>384</v>
+      </c>
+      <c r="J7" s="15">
+        <v>909</v>
+      </c>
+      <c r="K7" s="15">
+        <v>143</v>
+      </c>
+      <c r="L7" s="15">
+        <v>91</v>
+      </c>
+      <c r="M7" s="15">
+        <v>234</v>
+      </c>
+      <c r="N7" s="15">
+        <v>827</v>
+      </c>
+      <c r="O7" s="15">
+        <v>603</v>
+      </c>
+      <c r="P7" s="15">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="B8" s="15">
+        <v>71</v>
+      </c>
+      <c r="C8" s="15">
+        <v>63</v>
+      </c>
+      <c r="D8" s="15">
+        <v>134</v>
+      </c>
+      <c r="E8" s="15">
+        <v>1358</v>
+      </c>
+      <c r="F8" s="15">
+        <v>872</v>
+      </c>
+      <c r="G8" s="15">
+        <v>2230</v>
+      </c>
+      <c r="H8" s="15">
+        <v>2470</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1862</v>
+      </c>
+      <c r="J8" s="15">
+        <v>4332</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
+        <v>3899</v>
+      </c>
+      <c r="O8" s="15">
+        <v>2797</v>
+      </c>
+      <c r="P8" s="15">
+        <v>6696</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="15">
+        <v>2</v>
+      </c>
+      <c r="C9" s="15">
+        <v>2</v>
+      </c>
+      <c r="D9" s="15">
+        <v>4</v>
+      </c>
+      <c r="E9" s="15">
+        <v>99</v>
+      </c>
+      <c r="F9" s="15">
+        <v>63</v>
+      </c>
+      <c r="G9" s="15">
+        <v>162</v>
+      </c>
+      <c r="H9" s="15">
+        <v>330</v>
+      </c>
+      <c r="I9" s="15">
+        <v>232</v>
+      </c>
+      <c r="J9" s="15">
+        <v>562</v>
+      </c>
+      <c r="K9" s="15">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15">
+        <v>431</v>
+      </c>
+      <c r="O9" s="15">
+        <v>297</v>
+      </c>
+      <c r="P9" s="15">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="15">
+        <v>282</v>
+      </c>
+      <c r="C10" s="15">
+        <v>10</v>
+      </c>
+      <c r="D10" s="15">
+        <v>292</v>
+      </c>
+      <c r="E10" s="15">
+        <v>793</v>
+      </c>
+      <c r="F10" s="15">
+        <v>90</v>
+      </c>
+      <c r="G10" s="15">
+        <v>883</v>
+      </c>
+      <c r="H10" s="15">
+        <v>1331</v>
+      </c>
+      <c r="I10" s="15">
+        <v>384</v>
+      </c>
+      <c r="J10" s="15">
+        <v>1715</v>
+      </c>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="15">
+        <v>0</v>
+      </c>
+      <c r="N10" s="15">
+        <v>2406</v>
+      </c>
+      <c r="O10" s="15">
+        <v>484</v>
+      </c>
+      <c r="P10" s="15">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="15">
+        <v>37</v>
+      </c>
+      <c r="C11" s="15">
+        <v>12</v>
+      </c>
+      <c r="D11" s="15">
+        <v>49</v>
+      </c>
+      <c r="E11" s="15">
+        <v>134</v>
+      </c>
+      <c r="F11" s="15">
+        <v>79</v>
+      </c>
+      <c r="G11" s="15">
+        <v>213</v>
+      </c>
+      <c r="H11" s="15">
+        <v>249</v>
+      </c>
+      <c r="I11" s="15">
+        <v>214</v>
+      </c>
+      <c r="J11" s="15">
+        <v>463</v>
+      </c>
+      <c r="K11" s="15">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15">
+        <v>0</v>
+      </c>
+      <c r="N11" s="15">
+        <v>420</v>
+      </c>
+      <c r="O11" s="15">
+        <v>305</v>
+      </c>
+      <c r="P11" s="15">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="B12" s="15">
+        <v>14</v>
+      </c>
+      <c r="C12" s="15">
+        <v>11</v>
+      </c>
+      <c r="D12" s="15">
+        <v>25</v>
+      </c>
+      <c r="E12" s="15">
+        <v>163</v>
+      </c>
+      <c r="F12" s="15">
+        <v>130</v>
+      </c>
+      <c r="G12" s="15">
+        <v>293</v>
+      </c>
+      <c r="H12" s="15">
+        <v>463</v>
+      </c>
+      <c r="I12" s="15">
+        <v>493</v>
+      </c>
+      <c r="J12" s="15">
+        <v>956</v>
+      </c>
+      <c r="K12" s="15">
+        <v>0</v>
+      </c>
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>0</v>
+      </c>
+      <c r="N12" s="15">
+        <v>640</v>
+      </c>
+      <c r="O12" s="15">
+        <v>634</v>
+      </c>
+      <c r="P12" s="15">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="B13" s="15">
+        <v>85</v>
+      </c>
+      <c r="C13" s="15">
+        <v>24</v>
+      </c>
+      <c r="D13" s="15">
+        <v>109</v>
+      </c>
+      <c r="E13" s="15">
+        <v>185</v>
+      </c>
+      <c r="F13" s="15">
+        <v>130</v>
+      </c>
+      <c r="G13" s="15">
+        <v>315</v>
+      </c>
+      <c r="H13" s="15">
+        <v>528</v>
+      </c>
+      <c r="I13" s="15">
+        <v>629</v>
+      </c>
+      <c r="J13" s="15">
+        <v>1157</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0</v>
+      </c>
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0</v>
+      </c>
+      <c r="N13" s="15">
+        <v>798</v>
+      </c>
+      <c r="O13" s="15">
+        <v>783</v>
+      </c>
+      <c r="P13" s="15">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="B14" s="15">
         <v>15</v>
       </c>
-      <c r="D3" s="25">
-        <v>58</v>
-      </c>
-      <c r="E3" s="25">
-        <v>496</v>
-      </c>
-      <c r="F3" s="25">
-        <v>288</v>
-      </c>
-      <c r="G3" s="25">
-        <v>784</v>
-      </c>
-      <c r="H3" s="25">
-        <v>1399</v>
-      </c>
-      <c r="I3" s="25">
-        <v>1207</v>
-      </c>
-      <c r="J3" s="25">
-        <v>2606</v>
-      </c>
-      <c r="K3" s="25">
+      <c r="C14" s="15">
+        <v>11</v>
+      </c>
+      <c r="D14" s="15">
+        <v>26</v>
+      </c>
+      <c r="E14" s="15">
+        <v>146</v>
+      </c>
+      <c r="F14" s="15">
+        <v>64</v>
+      </c>
+      <c r="G14" s="15">
+        <v>210</v>
+      </c>
+      <c r="H14" s="15">
+        <v>687</v>
+      </c>
+      <c r="I14" s="15">
+        <v>436</v>
+      </c>
+      <c r="J14" s="15">
+        <v>1123</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="M14" s="15">
         <v>0</v>
       </c>
-      <c r="L3" s="25">
+      <c r="N14" s="15">
+        <v>848</v>
+      </c>
+      <c r="O14" s="15">
+        <v>511</v>
+      </c>
+      <c r="P14" s="15">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="B15" s="15">
+        <v>74</v>
+      </c>
+      <c r="C15" s="15">
+        <v>36</v>
+      </c>
+      <c r="D15" s="15">
+        <v>110</v>
+      </c>
+      <c r="E15" s="15">
+        <v>527</v>
+      </c>
+      <c r="F15" s="15">
+        <v>260</v>
+      </c>
+      <c r="G15" s="15">
+        <v>787</v>
+      </c>
+      <c r="H15" s="15">
+        <v>1782</v>
+      </c>
+      <c r="I15" s="15">
+        <v>1240</v>
+      </c>
+      <c r="J15" s="15">
+        <v>3022</v>
+      </c>
+      <c r="K15" s="15">
         <v>0</v>
       </c>
-      <c r="M3" s="25">
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="N3" s="25">
-        <v>1938</v>
-      </c>
-      <c r="O3" s="25">
-        <v>1510</v>
-      </c>
-      <c r="P3" s="25">
-        <v>3448</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
-        <v>447</v>
-      </c>
-      <c r="B4" s="25">
+      <c r="M15" s="15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="15">
+        <v>2383</v>
+      </c>
+      <c r="O15" s="15">
+        <v>1536</v>
+      </c>
+      <c r="P15" s="15">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="B16" s="15">
+        <v>4</v>
+      </c>
+      <c r="C16" s="15">
+        <v>6</v>
+      </c>
+      <c r="D16" s="15">
+        <v>10</v>
+      </c>
+      <c r="E16" s="15">
+        <v>28</v>
+      </c>
+      <c r="F16" s="15">
+        <v>19</v>
+      </c>
+      <c r="G16" s="15">
+        <v>47</v>
+      </c>
+      <c r="H16" s="15">
+        <v>100</v>
+      </c>
+      <c r="I16" s="15">
+        <v>69</v>
+      </c>
+      <c r="J16" s="15">
+        <v>169</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>0</v>
+      </c>
+      <c r="N16" s="15">
+        <v>132</v>
+      </c>
+      <c r="O16" s="15">
+        <v>94</v>
+      </c>
+      <c r="P16" s="15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="B17" s="15">
+        <v>30</v>
+      </c>
+      <c r="C17" s="15">
         <v>22</v>
       </c>
-      <c r="C4" s="25">
-        <v>13</v>
-      </c>
-      <c r="D4" s="25">
+      <c r="D17" s="15">
+        <v>52</v>
+      </c>
+      <c r="E17" s="15">
+        <v>393</v>
+      </c>
+      <c r="F17" s="15">
+        <v>209</v>
+      </c>
+      <c r="G17" s="15">
+        <v>602</v>
+      </c>
+      <c r="H17" s="15">
+        <v>1269</v>
+      </c>
+      <c r="I17" s="15">
+        <v>898</v>
+      </c>
+      <c r="J17" s="15">
+        <v>2167</v>
+      </c>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="15">
+        <v>0</v>
+      </c>
+      <c r="N17" s="15">
+        <v>1692</v>
+      </c>
+      <c r="O17" s="15">
+        <v>1129</v>
+      </c>
+      <c r="P17" s="15">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="B18" s="15">
+        <v>20</v>
+      </c>
+      <c r="C18" s="15">
+        <v>15</v>
+      </c>
+      <c r="D18" s="15">
         <v>35</v>
       </c>
-      <c r="E4" s="25">
-        <v>252</v>
-      </c>
-      <c r="F4" s="25">
+      <c r="E18" s="15">
         <v>110</v>
       </c>
-      <c r="G4" s="25">
-        <v>362</v>
-      </c>
-      <c r="H4" s="25">
-        <v>706</v>
-      </c>
-      <c r="I4" s="25">
-        <v>390</v>
-      </c>
-      <c r="J4" s="25">
-        <v>1096</v>
-      </c>
-      <c r="K4" s="25">
+      <c r="F18" s="15">
+        <v>65</v>
+      </c>
+      <c r="G18" s="15">
+        <v>175</v>
+      </c>
+      <c r="H18" s="15">
+        <v>466</v>
+      </c>
+      <c r="I18" s="15">
+        <v>284</v>
+      </c>
+      <c r="J18" s="15">
+        <v>750</v>
+      </c>
+      <c r="K18" s="15">
         <v>0</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L18" s="15">
         <v>0</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M18" s="15">
         <v>0</v>
       </c>
-      <c r="N4" s="25">
-        <v>980</v>
-      </c>
-      <c r="O4" s="25">
-        <v>513</v>
-      </c>
-      <c r="P4" s="25">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="26" t="s">
-        <v>448</v>
-      </c>
-      <c r="B5" s="25">
-        <v>27</v>
-      </c>
-      <c r="C5" s="25">
-        <v>9</v>
-      </c>
-      <c r="D5" s="25">
-        <v>36</v>
-      </c>
-      <c r="E5" s="25">
-        <v>116</v>
-      </c>
-      <c r="F5" s="25">
-        <v>182</v>
-      </c>
-      <c r="G5" s="25">
-        <v>298</v>
-      </c>
-      <c r="H5" s="25">
-        <v>249</v>
-      </c>
-      <c r="I5" s="25">
-        <v>175</v>
-      </c>
-      <c r="J5" s="25">
-        <v>424</v>
-      </c>
-      <c r="K5" s="25">
-        <v>0</v>
-      </c>
-      <c r="L5" s="25">
-        <v>0</v>
-      </c>
-      <c r="M5" s="25">
-        <v>0</v>
-      </c>
-      <c r="N5" s="25">
-        <v>392</v>
-      </c>
-      <c r="O5" s="25">
-        <v>366</v>
-      </c>
-      <c r="P5" s="25">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="26" t="s">
-        <v>449</v>
-      </c>
-      <c r="B6" s="25">
-        <v>20</v>
-      </c>
-      <c r="C6" s="25">
-        <v>9</v>
-      </c>
-      <c r="D6" s="25">
-        <v>29</v>
-      </c>
-      <c r="E6" s="25">
-        <v>97</v>
-      </c>
-      <c r="F6" s="25">
-        <v>62</v>
-      </c>
-      <c r="G6" s="25">
-        <v>159</v>
-      </c>
-      <c r="H6" s="25">
-        <v>185</v>
-      </c>
-      <c r="I6" s="25">
-        <v>168</v>
-      </c>
-      <c r="J6" s="25">
-        <v>353</v>
-      </c>
-      <c r="K6" s="25">
-        <v>0</v>
-      </c>
-      <c r="L6" s="25">
-        <v>0</v>
-      </c>
-      <c r="M6" s="25">
-        <v>0</v>
-      </c>
-      <c r="N6" s="25">
-        <v>302</v>
-      </c>
-      <c r="O6" s="25">
-        <v>239</v>
-      </c>
-      <c r="P6" s="25">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
-        <v>450</v>
-      </c>
-      <c r="B7" s="25">
-        <v>20</v>
-      </c>
-      <c r="C7" s="25">
-        <v>45</v>
-      </c>
-      <c r="D7" s="25">
-        <v>65</v>
-      </c>
-      <c r="E7" s="25">
-        <v>139</v>
-      </c>
-      <c r="F7" s="25">
-        <v>83</v>
-      </c>
-      <c r="G7" s="25">
-        <v>222</v>
-      </c>
-      <c r="H7" s="25">
-        <v>525</v>
-      </c>
-      <c r="I7" s="25">
-        <v>384</v>
-      </c>
-      <c r="J7" s="25">
-        <v>909</v>
-      </c>
-      <c r="K7" s="25">
+      <c r="N18" s="15">
+        <v>596</v>
+      </c>
+      <c r="O18" s="15">
+        <v>364</v>
+      </c>
+      <c r="P18" s="15">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="18"/>
+      <c r="B19" s="19">
+        <v>766</v>
+      </c>
+      <c r="C19" s="19">
+        <v>303</v>
+      </c>
+      <c r="D19" s="19">
+        <v>1069</v>
+      </c>
+      <c r="E19" s="19">
+        <v>5036</v>
+      </c>
+      <c r="F19" s="19">
+        <v>2706</v>
+      </c>
+      <c r="G19" s="19">
+        <v>7742</v>
+      </c>
+      <c r="H19" s="19">
+        <v>12739</v>
+      </c>
+      <c r="I19" s="19">
+        <v>9065</v>
+      </c>
+      <c r="J19" s="19">
+        <v>21804</v>
+      </c>
+      <c r="K19" s="19">
         <v>143</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L19" s="19">
         <v>91</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M19" s="19">
         <v>234</v>
       </c>
-      <c r="N7" s="25">
-        <v>827</v>
-      </c>
-      <c r="O7" s="25">
-        <v>603</v>
-      </c>
-      <c r="P7" s="25">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="26" t="s">
-        <v>451</v>
-      </c>
-      <c r="B8" s="25">
-        <v>71</v>
-      </c>
-      <c r="C8" s="25">
-        <v>63</v>
-      </c>
-      <c r="D8" s="25">
-        <v>134</v>
-      </c>
-      <c r="E8" s="25">
-        <v>1358</v>
-      </c>
-      <c r="F8" s="25">
-        <v>872</v>
-      </c>
-      <c r="G8" s="25">
-        <v>2230</v>
-      </c>
-      <c r="H8" s="25">
-        <v>2470</v>
-      </c>
-      <c r="I8" s="25">
-        <v>1862</v>
-      </c>
-      <c r="J8" s="25">
-        <v>4332</v>
-      </c>
-      <c r="K8" s="25">
-        <v>0</v>
-      </c>
-      <c r="L8" s="25">
-        <v>0</v>
-      </c>
-      <c r="M8" s="25">
-        <v>0</v>
-      </c>
-      <c r="N8" s="25">
-        <v>3899</v>
-      </c>
-      <c r="O8" s="25">
-        <v>2797</v>
-      </c>
-      <c r="P8" s="25">
-        <v>6696</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="B9" s="25">
-        <v>2</v>
-      </c>
-      <c r="C9" s="25">
-        <v>2</v>
-      </c>
-      <c r="D9" s="25">
-        <v>4</v>
-      </c>
-      <c r="E9" s="25">
-        <v>99</v>
-      </c>
-      <c r="F9" s="25">
-        <v>63</v>
-      </c>
-      <c r="G9" s="25">
-        <v>162</v>
-      </c>
-      <c r="H9" s="25">
-        <v>330</v>
-      </c>
-      <c r="I9" s="25">
-        <v>232</v>
-      </c>
-      <c r="J9" s="25">
-        <v>562</v>
-      </c>
-      <c r="K9" s="25">
-        <v>0</v>
-      </c>
-      <c r="L9" s="25">
-        <v>0</v>
-      </c>
-      <c r="M9" s="25">
-        <v>0</v>
-      </c>
-      <c r="N9" s="25">
-        <v>431</v>
-      </c>
-      <c r="O9" s="25">
-        <v>297</v>
-      </c>
-      <c r="P9" s="25">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="26" t="s">
-        <v>453</v>
-      </c>
-      <c r="B10" s="25">
-        <v>282</v>
-      </c>
-      <c r="C10" s="25">
-        <v>10</v>
-      </c>
-      <c r="D10" s="25">
-        <v>292</v>
-      </c>
-      <c r="E10" s="25">
-        <v>793</v>
-      </c>
-      <c r="F10" s="25">
-        <v>90</v>
-      </c>
-      <c r="G10" s="25">
-        <v>883</v>
-      </c>
-      <c r="H10" s="25">
-        <v>1331</v>
-      </c>
-      <c r="I10" s="25">
-        <v>384</v>
-      </c>
-      <c r="J10" s="25">
-        <v>1715</v>
-      </c>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="25">
-        <v>0</v>
-      </c>
-      <c r="N10" s="25">
-        <v>2406</v>
-      </c>
-      <c r="O10" s="25">
-        <v>484</v>
-      </c>
-      <c r="P10" s="25">
-        <v>2890</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
-        <v>454</v>
-      </c>
-      <c r="B11" s="25">
-        <v>37</v>
-      </c>
-      <c r="C11" s="25">
-        <v>12</v>
-      </c>
-      <c r="D11" s="25">
-        <v>49</v>
-      </c>
-      <c r="E11" s="25">
-        <v>134</v>
-      </c>
-      <c r="F11" s="25">
-        <v>79</v>
-      </c>
-      <c r="G11" s="25">
-        <v>213</v>
-      </c>
-      <c r="H11" s="25">
-        <v>249</v>
-      </c>
-      <c r="I11" s="25">
-        <v>214</v>
-      </c>
-      <c r="J11" s="25">
-        <v>463</v>
-      </c>
-      <c r="K11" s="25">
-        <v>0</v>
-      </c>
-      <c r="L11" s="25">
-        <v>0</v>
-      </c>
-      <c r="M11" s="25">
-        <v>0</v>
-      </c>
-      <c r="N11" s="25">
-        <v>420</v>
-      </c>
-      <c r="O11" s="25">
-        <v>305</v>
-      </c>
-      <c r="P11" s="25">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="B12" s="25">
-        <v>14</v>
-      </c>
-      <c r="C12" s="25">
-        <v>11</v>
-      </c>
-      <c r="D12" s="25">
-        <v>25</v>
-      </c>
-      <c r="E12" s="25">
-        <v>163</v>
-      </c>
-      <c r="F12" s="25">
-        <v>130</v>
-      </c>
-      <c r="G12" s="25">
-        <v>293</v>
-      </c>
-      <c r="H12" s="25">
-        <v>463</v>
-      </c>
-      <c r="I12" s="25">
-        <v>493</v>
-      </c>
-      <c r="J12" s="25">
-        <v>956</v>
-      </c>
-      <c r="K12" s="25">
-        <v>0</v>
-      </c>
-      <c r="L12" s="25">
-        <v>0</v>
-      </c>
-      <c r="M12" s="25">
-        <v>0</v>
-      </c>
-      <c r="N12" s="25">
-        <v>640</v>
-      </c>
-      <c r="O12" s="25">
-        <v>634</v>
-      </c>
-      <c r="P12" s="25">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
-        <v>456</v>
-      </c>
-      <c r="B13" s="25">
-        <v>85</v>
-      </c>
-      <c r="C13" s="25">
-        <v>24</v>
-      </c>
-      <c r="D13" s="25">
-        <v>109</v>
-      </c>
-      <c r="E13" s="25">
-        <v>185</v>
-      </c>
-      <c r="F13" s="25">
-        <v>130</v>
-      </c>
-      <c r="G13" s="25">
-        <v>315</v>
-      </c>
-      <c r="H13" s="25">
-        <v>528</v>
-      </c>
-      <c r="I13" s="25">
-        <v>629</v>
-      </c>
-      <c r="J13" s="25">
-        <v>1157</v>
-      </c>
-      <c r="K13" s="25">
-        <v>0</v>
-      </c>
-      <c r="L13" s="25">
-        <v>0</v>
-      </c>
-      <c r="M13" s="25">
-        <v>0</v>
-      </c>
-      <c r="N13" s="25">
-        <v>798</v>
-      </c>
-      <c r="O13" s="25">
-        <v>783</v>
-      </c>
-      <c r="P13" s="25">
-        <v>1581</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="B14" s="25">
-        <v>15</v>
-      </c>
-      <c r="C14" s="25">
-        <v>11</v>
-      </c>
-      <c r="D14" s="25">
-        <v>26</v>
-      </c>
-      <c r="E14" s="25">
-        <v>146</v>
-      </c>
-      <c r="F14" s="25">
-        <v>64</v>
-      </c>
-      <c r="G14" s="25">
-        <v>210</v>
-      </c>
-      <c r="H14" s="25">
-        <v>687</v>
-      </c>
-      <c r="I14" s="25">
-        <v>436</v>
-      </c>
-      <c r="J14" s="25">
-        <v>1123</v>
-      </c>
-      <c r="K14" s="25" t="s">
-        <v>458</v>
-      </c>
-      <c r="L14" s="25" t="s">
-        <v>458</v>
-      </c>
-      <c r="M14" s="25">
-        <v>0</v>
-      </c>
-      <c r="N14" s="25">
-        <v>848</v>
-      </c>
-      <c r="O14" s="25">
-        <v>511</v>
-      </c>
-      <c r="P14" s="25">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="B15" s="25">
-        <v>74</v>
-      </c>
-      <c r="C15" s="25">
-        <v>36</v>
-      </c>
-      <c r="D15" s="25">
-        <v>110</v>
-      </c>
-      <c r="E15" s="25">
-        <v>527</v>
-      </c>
-      <c r="F15" s="25">
-        <v>260</v>
-      </c>
-      <c r="G15" s="25">
-        <v>787</v>
-      </c>
-      <c r="H15" s="25">
-        <v>1782</v>
-      </c>
-      <c r="I15" s="25">
-        <v>1240</v>
-      </c>
-      <c r="J15" s="25">
-        <v>3022</v>
-      </c>
-      <c r="K15" s="25">
-        <v>0</v>
-      </c>
-      <c r="L15" s="25">
-        <v>0</v>
-      </c>
-      <c r="M15" s="25">
-        <v>0</v>
-      </c>
-      <c r="N15" s="25">
-        <v>2383</v>
-      </c>
-      <c r="O15" s="25">
-        <v>1536</v>
-      </c>
-      <c r="P15" s="25">
-        <v>3919</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="B16" s="25">
-        <v>4</v>
-      </c>
-      <c r="C16" s="25">
-        <v>6</v>
-      </c>
-      <c r="D16" s="25">
-        <v>10</v>
-      </c>
-      <c r="E16" s="25">
-        <v>28</v>
-      </c>
-      <c r="F16" s="25">
-        <v>19</v>
-      </c>
-      <c r="G16" s="25">
-        <v>47</v>
-      </c>
-      <c r="H16" s="25">
-        <v>100</v>
-      </c>
-      <c r="I16" s="25">
-        <v>69</v>
-      </c>
-      <c r="J16" s="25">
-        <v>169</v>
-      </c>
-      <c r="K16" s="25">
-        <v>0</v>
-      </c>
-      <c r="L16" s="25">
-        <v>0</v>
-      </c>
-      <c r="M16" s="25">
-        <v>0</v>
-      </c>
-      <c r="N16" s="25">
-        <v>132</v>
-      </c>
-      <c r="O16" s="25">
-        <v>94</v>
-      </c>
-      <c r="P16" s="25">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="B17" s="25">
-        <v>30</v>
-      </c>
-      <c r="C17" s="25">
-        <v>22</v>
-      </c>
-      <c r="D17" s="25">
-        <v>52</v>
-      </c>
-      <c r="E17" s="25">
-        <v>393</v>
-      </c>
-      <c r="F17" s="25">
-        <v>209</v>
-      </c>
-      <c r="G17" s="25">
-        <v>602</v>
-      </c>
-      <c r="H17" s="25">
-        <v>1269</v>
-      </c>
-      <c r="I17" s="25">
-        <v>898</v>
-      </c>
-      <c r="J17" s="25">
-        <v>2167</v>
-      </c>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="25">
-        <v>0</v>
-      </c>
-      <c r="N17" s="25">
-        <v>1692</v>
-      </c>
-      <c r="O17" s="25">
-        <v>1129</v>
-      </c>
-      <c r="P17" s="25">
-        <v>2821</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
-        <v>462</v>
-      </c>
-      <c r="B18" s="25">
-        <v>20</v>
-      </c>
-      <c r="C18" s="25">
-        <v>15</v>
-      </c>
-      <c r="D18" s="25">
-        <v>35</v>
-      </c>
-      <c r="E18" s="25">
-        <v>110</v>
-      </c>
-      <c r="F18" s="25">
-        <v>65</v>
-      </c>
-      <c r="G18" s="25">
-        <v>175</v>
-      </c>
-      <c r="H18" s="25">
-        <v>466</v>
-      </c>
-      <c r="I18" s="25">
-        <v>284</v>
-      </c>
-      <c r="J18" s="25">
-        <v>750</v>
-      </c>
-      <c r="K18" s="25">
-        <v>0</v>
-      </c>
-      <c r="L18" s="25">
-        <v>0</v>
-      </c>
-      <c r="M18" s="25">
-        <v>0</v>
-      </c>
-      <c r="N18" s="25">
-        <v>596</v>
-      </c>
-      <c r="O18" s="25">
-        <v>364</v>
-      </c>
-      <c r="P18" s="25">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29">
-        <v>766</v>
-      </c>
-      <c r="C19" s="29">
-        <v>303</v>
-      </c>
-      <c r="D19" s="29">
-        <v>1069</v>
-      </c>
-      <c r="E19" s="29">
-        <v>5036</v>
-      </c>
-      <c r="F19" s="29">
-        <v>2706</v>
-      </c>
-      <c r="G19" s="29">
-        <v>7742</v>
-      </c>
-      <c r="H19" s="29">
-        <v>12739</v>
-      </c>
-      <c r="I19" s="29">
-        <v>9065</v>
-      </c>
-      <c r="J19" s="29">
-        <v>21804</v>
-      </c>
-      <c r="K19" s="29">
-        <v>143</v>
-      </c>
-      <c r="L19" s="29">
-        <v>91</v>
-      </c>
-      <c r="M19" s="29">
-        <v>234</v>
-      </c>
-      <c r="N19" s="29">
+      <c r="N19" s="19">
         <v>18684</v>
       </c>
-      <c r="O19" s="29">
+      <c r="O19" s="19">
         <v>12165</v>
       </c>
-      <c r="P19" s="29">
+      <c r="P19" s="19">
         <v>30849</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
